--- a/Backtest/12-03-21/NASDAQstock_12-03-21period252RS90.xlsx
+++ b/Backtest/12-03-21/NASDAQstock_12-03-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="185">
   <si>
     <t>Stock</t>
   </si>
@@ -127,241 +127,448 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>FRHC</t>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>UNFI</t>
+  </si>
+  <si>
+    <t>NMRK</t>
+  </si>
+  <si>
+    <t>CDMO</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>CALX</t>
+  </si>
+  <si>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>ATEN</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>SITE</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>PECO</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>IMO</t>
+  </si>
+  <si>
+    <t>HLIO</t>
+  </si>
+  <si>
+    <t>ICL</t>
+  </si>
+  <si>
+    <t>SHYF</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>DFIN</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>SKY</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>WSC</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>STN</t>
   </si>
   <si>
     <t>ARCB</t>
   </si>
   <si>
-    <t>CROX</t>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>ATKR</t>
+  </si>
+  <si>
+    <t>MXL</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>CDXS</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>NVEE</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>AMBA</t>
+  </si>
+  <si>
+    <t>SPG</t>
+  </si>
+  <si>
+    <t>ROG</t>
+  </si>
+  <si>
+    <t>LPX</t>
+  </si>
+  <si>
+    <t>CHRD</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>CACC</t>
+  </si>
+  <si>
+    <t>LSCC</t>
+  </si>
+  <si>
+    <t>VBTX</t>
+  </si>
+  <si>
+    <t>AMG</t>
+  </si>
+  <si>
+    <t>MGPI</t>
+  </si>
+  <si>
+    <t>NSA</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>KEN</t>
+  </si>
+  <si>
+    <t>IMKTA</t>
+  </si>
+  <si>
+    <t>FOXF</t>
+  </si>
+  <si>
+    <t>CCS</t>
+  </si>
+  <si>
+    <t>KFRC</t>
+  </si>
+  <si>
+    <t>TGLS</t>
   </si>
   <si>
     <t>LOB</t>
   </si>
   <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>SONO</t>
-  </si>
-  <si>
-    <t>ETSY</t>
-  </si>
-  <si>
-    <t>HRI</t>
-  </si>
-  <si>
-    <t>IAC</t>
-  </si>
-  <si>
-    <t>TFIN</t>
-  </si>
-  <si>
-    <t>OMI</t>
-  </si>
-  <si>
-    <t>RVLV</t>
-  </si>
-  <si>
-    <t>CALX</t>
-  </si>
-  <si>
-    <t>SID</t>
-  </si>
-  <si>
-    <t>REZI</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>FCX</t>
-  </si>
-  <si>
-    <t>XPEL</t>
-  </si>
-  <si>
-    <t>GEAR</t>
-  </si>
-  <si>
-    <t>WES</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>HBM</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>SAM</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>TROX</t>
-  </si>
-  <si>
-    <t>MED</t>
+    <t>CNOB</t>
+  </si>
+  <si>
+    <t>KAI</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>EXR</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>PIPR</t>
+  </si>
+  <si>
+    <t>MP</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-05-04</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-05-05</t>
-  </si>
-  <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-05-10</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>2022-01-26</t>
+  </si>
+  <si>
+    <t>2021-12-08</t>
+  </si>
+  <si>
+    <t>2022-02-11</t>
+  </si>
+  <si>
+    <t>2021-12-07</t>
+  </si>
+  <si>
+    <t>2022-02-02</t>
+  </si>
+  <si>
+    <t>2022-01-27</t>
+  </si>
+  <si>
+    <t>2022-02-01</t>
+  </si>
+  <si>
+    <t>2022-02-24</t>
+  </si>
+  <si>
+    <t>2022-02-16</t>
+  </si>
+  <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
+    <t>2022-02-10</t>
+  </si>
+  <si>
+    <t>2022-03-03</t>
+  </si>
+  <si>
+    <t>2022-02-28</t>
+  </si>
+  <si>
+    <t>2022-02-09</t>
+  </si>
+  <si>
+    <t>2022-02-07</t>
+  </si>
+  <si>
+    <t>2022-03-01</t>
+  </si>
+  <si>
+    <t>2022-02-22</t>
+  </si>
+  <si>
+    <t>2022-02-08</t>
+  </si>
+  <si>
+    <t>2022-02-17</t>
+  </si>
+  <si>
+    <t>2022-02-03</t>
+  </si>
+  <si>
+    <t>2022-02-23</t>
+  </si>
+  <si>
+    <t>2022-01-31</t>
+  </si>
+  <si>
+    <t>2022-01-24</t>
+  </si>
+  <si>
+    <t>2022-01-25</t>
+  </si>
+  <si>
+    <t>2022-03-31</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
   </si>
   <si>
     <t>Industrials</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>Consumer Defensive</t>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Food Distribution</t>
+  </si>
+  <si>
+    <t>Real Estate Services</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Communication Equipment</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>REIT - Retail</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Integrated</t>
   </si>
   <si>
     <t>Specialty Industrial Machinery</t>
   </si>
   <si>
+    <t>Agricultural Inputs</t>
+  </si>
+  <si>
+    <t>Farm &amp; Heavy Construction Machinery</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Auto &amp; Truck Dealerships</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Consulting Services</t>
+  </si>
+  <si>
+    <t>Banks - Regional</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Credit Services</t>
+  </si>
+  <si>
+    <t>Beverages - Wineries &amp; Distilleries</t>
+  </si>
+  <si>
+    <t>REIT - Industrial</t>
+  </si>
+  <si>
+    <t>Beverages - Non-Alcoholic</t>
+  </si>
+  <si>
+    <t>Utilities - Independent Power Producers</t>
+  </si>
+  <si>
+    <t>Grocery Stores</t>
+  </si>
+  <si>
+    <t>Real Estate - Development</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Employment Services</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Medical Care Facilities</t>
+  </si>
+  <si>
     <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Trucking</t>
-  </si>
-  <si>
-    <t>Footwear &amp; Accessories</t>
-  </si>
-  <si>
-    <t>Banks - Regional</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Consumer Electronics</t>
-  </si>
-  <si>
-    <t>Internet Retail</t>
-  </si>
-  <si>
-    <t>Rental &amp; Leasing Services</t>
-  </si>
-  <si>
-    <t>Internet Content &amp; Information</t>
-  </si>
-  <si>
-    <t>Medical Distribution</t>
-  </si>
-  <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Mortgage Finance</t>
-  </si>
-  <si>
-    <t>Auto &amp; Truck Dealerships</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
-    <t>Advertising Agencies</t>
-  </si>
-  <si>
-    <t>Beverages - Brewers</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Personal Services</t>
   </si>
 </sst>
 </file>
@@ -719,7 +926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK34"/>
+  <dimension ref="A1:AK70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -840,109 +1047,109 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>95.65217391304348</v>
+        <v>91.86333215921098</v>
       </c>
       <c r="C2">
-        <v>2311</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>153.41</v>
+        <v>361.53</v>
       </c>
       <c r="E2">
-        <v>3.59</v>
+        <v>4.06</v>
       </c>
       <c r="F2">
-        <v>-0.6651782943671583</v>
+        <v>1.46035529674958</v>
       </c>
       <c r="G2">
-        <v>3.73</v>
+        <v>3.35</v>
       </c>
       <c r="H2">
-        <v>-0.2443319563106113</v>
+        <v>0.9532703259192202</v>
       </c>
       <c r="I2">
-        <v>151.4480041503906</v>
+        <v>369.5513366699219</v>
       </c>
       <c r="J2">
-        <v>147.182999420166</v>
+        <v>368.6509979248047</v>
       </c>
       <c r="K2">
-        <v>138.9390005493164</v>
+        <v>325.4172006225586</v>
       </c>
       <c r="L2">
-        <v>90.0706001663208</v>
+        <v>249.6318838500977</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T2">
-        <v>0.5555555555555555</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>179.83</v>
       </c>
       <c r="Y2">
-        <v>160.53</v>
+        <v>414.5</v>
       </c>
       <c r="Z2">
-        <v>4.29</v>
+        <v>870.86</v>
       </c>
       <c r="AA2">
-        <v>-3.76</v>
+        <v>-104.17</v>
       </c>
       <c r="AB2">
-        <v>440.99</v>
+        <v>298.99</v>
       </c>
       <c r="AC2">
-        <v>2933.33</v>
+        <v>440</v>
       </c>
       <c r="AD2">
-        <v>2.39</v>
+        <v>5.95</v>
       </c>
       <c r="AE2">
-        <v>1074.19</v>
+        <v>37.3</v>
       </c>
       <c r="AF2">
-        <v>8.77</v>
+        <v>156.56</v>
       </c>
       <c r="AG2">
-        <v>137.5</v>
+        <v>53.3</v>
       </c>
       <c r="AH2" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="AI2" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="AJ2" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="AK2">
-        <v>75.47027334530092</v>
+        <v>77.03929816020027</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -950,43 +1157,43 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>92.40109674892284</v>
+        <v>97.12927087002465</v>
       </c>
       <c r="C3">
-        <v>1252</v>
+        <v>1920</v>
       </c>
       <c r="D3">
-        <v>53.29</v>
+        <v>49.53</v>
       </c>
       <c r="E3">
-        <v>3.09</v>
+        <v>2.44</v>
       </c>
       <c r="F3">
-        <v>-0.9912460857236085</v>
+        <v>-0.2218223111509562</v>
       </c>
       <c r="G3">
-        <v>4.14</v>
+        <v>3.93</v>
       </c>
       <c r="H3">
-        <v>0.1450451189405752</v>
+        <v>1.716878781549468</v>
       </c>
       <c r="I3">
-        <v>51.02399978637695</v>
+        <v>49.05</v>
       </c>
       <c r="J3">
-        <v>54.57950000762939</v>
+        <v>50.0935001373291</v>
       </c>
       <c r="K3">
-        <v>52.55660003662109</v>
+        <v>46.94540000915527</v>
       </c>
       <c r="L3">
-        <v>32.82184995651245</v>
+        <v>37.86129994392395</v>
       </c>
       <c r="M3">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="N3">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1007,52 +1214,52 @@
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>11.25</v>
+        <v>14.55</v>
       </c>
       <c r="Y3">
-        <v>61.77</v>
+        <v>52.99</v>
       </c>
       <c r="Z3">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>70</v>
+        <v>1.99</v>
+      </c>
+      <c r="AA3">
+        <v>5.59</v>
       </c>
       <c r="AB3">
-        <v>254.55</v>
+        <v>151.76</v>
       </c>
       <c r="AC3">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="AD3">
-        <v>18.76</v>
+        <v>2.71</v>
       </c>
       <c r="AE3">
-        <v>80</v>
+        <v>-11.63</v>
       </c>
       <c r="AF3">
-        <v>-4.76</v>
+        <v>-18.1</v>
       </c>
       <c r="AG3">
-        <v>2000</v>
+        <v>5350</v>
       </c>
       <c r="AH3" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="AI3" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="AJ3" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="AK3">
-        <v>75.09895319483715</v>
+        <v>73.86732140655572</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1060,46 +1267,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>93.81120250685468</v>
+        <v>94.22331806974287</v>
       </c>
       <c r="C4">
-        <v>2027</v>
+        <v>1122</v>
       </c>
       <c r="D4">
-        <v>72.47</v>
+        <v>15.59</v>
       </c>
       <c r="E4">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="F4">
-        <v>-0.8934257483166732</v>
+        <v>0.4635093068825959</v>
       </c>
       <c r="G4">
-        <v>2.81</v>
+        <v>2.52</v>
       </c>
       <c r="H4">
-        <v>-1.118056125166933</v>
+        <v>-0.1394797054137207</v>
       </c>
       <c r="I4">
-        <v>69.87588348388672</v>
+        <v>15.58841953277588</v>
       </c>
       <c r="J4">
-        <v>60.85350837707519</v>
+        <v>15.93576698303223</v>
       </c>
       <c r="K4">
-        <v>52.48453742980957</v>
+        <v>14.89340129852295</v>
       </c>
       <c r="L4">
-        <v>37.15868803024292</v>
+        <v>12.38609680175781</v>
       </c>
       <c r="M4">
-        <v>1.15</v>
+        <v>0.98</v>
       </c>
       <c r="N4">
-        <v>1.33</v>
-      </c>
-      <c r="O4" t="s">
-        <v>14</v>
+        <v>1.05</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1111,61 +1315,61 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>13.19</v>
+        <v>6.32</v>
       </c>
       <c r="Y4">
-        <v>73.81</v>
+        <v>17.36</v>
       </c>
       <c r="Z4">
-        <v>1.11</v>
-      </c>
-      <c r="AA4">
-        <v>25.92</v>
+        <v>2.84</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>107</v>
       </c>
       <c r="AB4">
-        <v>71.78</v>
+        <v>909.6799999999999</v>
       </c>
       <c r="AC4">
-        <v>1271.43</v>
+        <v>2233.33</v>
       </c>
       <c r="AD4">
-        <v>2.89</v>
+        <v>10.05</v>
       </c>
       <c r="AE4">
-        <v>-16.52</v>
+        <v>-72.77</v>
       </c>
       <c r="AF4">
-        <v>85.48</v>
+        <v>1282.35</v>
       </c>
       <c r="AG4">
-        <v>785.71</v>
+        <v>666.67</v>
       </c>
       <c r="AH4" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="AI4" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AJ4" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="AK4">
-        <v>63.26059378587545</v>
+        <v>73.00856407600178</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1173,43 +1377,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>93.86995691343517</v>
+        <v>97.78090877069391</v>
       </c>
       <c r="C5">
-        <v>1267.5</v>
+        <v>1498</v>
       </c>
       <c r="D5">
-        <v>82.56</v>
+        <v>31.5</v>
       </c>
       <c r="E5">
-        <v>2.71</v>
+        <v>2.14</v>
       </c>
       <c r="F5">
-        <v>-1.239057607154511</v>
+        <v>-0.5333366829843886</v>
       </c>
       <c r="G5">
-        <v>3.12</v>
+        <v>3.61</v>
       </c>
       <c r="H5">
-        <v>-0.8236490682696939</v>
+        <v>1.295577564650021</v>
       </c>
       <c r="I5">
-        <v>77.56200103759765</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="J5">
-        <v>78.8645004272461</v>
+        <v>32.52049989700318</v>
       </c>
       <c r="K5">
-        <v>74.66680023193359</v>
+        <v>28.0796000289917</v>
       </c>
       <c r="L5">
-        <v>52.44200006484985</v>
+        <v>23.44795000076294</v>
       </c>
       <c r="M5">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="N5">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1218,64 +1422,64 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>9.444444444444443</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>8.4</v>
+        <v>10.04</v>
       </c>
       <c r="Y5">
-        <v>84.09</v>
+        <v>34.51</v>
       </c>
       <c r="Z5">
-        <v>4.29</v>
+        <v>1.63</v>
       </c>
       <c r="AA5">
-        <v>-61.34</v>
+        <v>-0.55</v>
       </c>
       <c r="AB5">
-        <v>149.46</v>
+        <v>183.33</v>
       </c>
       <c r="AC5">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="AD5">
-        <v>63.08</v>
+        <v>14.12</v>
       </c>
       <c r="AE5">
-        <v>195.65</v>
+        <v>600</v>
       </c>
       <c r="AF5">
-        <v>9.52</v>
+        <v>-300</v>
       </c>
       <c r="AG5">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="AI5" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="AJ5" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="AK5">
-        <v>62.63380323879485</v>
+        <v>70.70496351984605</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1283,58 +1487,61 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>96.3963963963964</v>
+        <v>97.69284959492779</v>
       </c>
       <c r="C6">
-        <v>2237</v>
+        <v>1331</v>
       </c>
       <c r="D6">
-        <v>60.03</v>
+        <v>291.7</v>
       </c>
       <c r="E6">
-        <v>4.48</v>
+        <v>6.54</v>
       </c>
       <c r="F6">
-        <v>-0.08477762575267642</v>
+        <v>4.035540770572624</v>
       </c>
       <c r="G6">
-        <v>3.78</v>
+        <v>4.61</v>
       </c>
       <c r="H6">
-        <v>-0.1968469471336375</v>
+        <v>2.612143867460794</v>
       </c>
       <c r="I6">
-        <v>56.53291931152344</v>
+        <v>299.7980102539062</v>
       </c>
       <c r="J6">
-        <v>52.28550834655762</v>
+        <v>277.7520011901855</v>
       </c>
       <c r="K6">
-        <v>48.03873901367187</v>
+        <v>247.3866015625</v>
       </c>
       <c r="L6">
-        <v>31.94801044940948</v>
+        <v>159.4394003677368</v>
       </c>
       <c r="M6">
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>1.18</v>
+        <v>1.21</v>
+      </c>
+      <c r="O6" t="s">
+        <v>106</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>4.444444444444444</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1343,49 +1550,49 @@
         <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>7.45</v>
+        <v>75.81</v>
       </c>
       <c r="Y6">
-        <v>60.26</v>
+        <v>321</v>
       </c>
       <c r="Z6">
-        <v>1.96</v>
+        <v>4.34</v>
       </c>
       <c r="AA6">
-        <v>45.63</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AB6">
-        <v>461.54</v>
+        <v>250.94</v>
       </c>
       <c r="AC6">
-        <v>484.21</v>
+        <v>356.25</v>
       </c>
       <c r="AD6">
-        <v>5.21</v>
+        <v>4.28</v>
       </c>
       <c r="AE6">
-        <v>-12.05</v>
+        <v>563.64</v>
       </c>
       <c r="AF6">
-        <v>822.22</v>
+        <v>155</v>
       </c>
       <c r="AG6">
-        <v>147.37</v>
+        <v>-225</v>
       </c>
       <c r="AH6" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AI6" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="AJ6" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="AK6">
-        <v>62.11339417622226</v>
+        <v>65.67086041893918</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1393,43 +1600,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>93.18448883666275</v>
+        <v>97.44628390278267</v>
       </c>
       <c r="C7">
-        <v>1785</v>
+        <v>1901</v>
       </c>
       <c r="D7">
-        <v>46.11</v>
+        <v>68.16</v>
       </c>
       <c r="E7">
-        <v>4.26</v>
+        <v>2.69</v>
       </c>
       <c r="F7">
-        <v>-0.2282474539495149</v>
+        <v>0.03777299871023774</v>
       </c>
       <c r="G7">
-        <v>3.69</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
-        <v>-0.2823199636521905</v>
+        <v>0.6241287502165273</v>
       </c>
       <c r="I7">
-        <v>43.0639991760254</v>
+        <v>67.46400146484375</v>
       </c>
       <c r="J7">
-        <v>46.92449951171875</v>
+        <v>71.2265007019043</v>
       </c>
       <c r="K7">
-        <v>42.46619964599609</v>
+        <v>62.3770004272461</v>
       </c>
       <c r="L7">
-        <v>24.85469995975494</v>
+        <v>48.62190017700195</v>
       </c>
       <c r="M7">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="N7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1438,64 +1645,64 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>5.555555555555555</v>
+        <v>4.444444444444444</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>6.78</v>
+        <v>22.59</v>
       </c>
       <c r="Y7">
-        <v>53.98</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z7">
-        <v>1.46</v>
+        <v>3.36</v>
       </c>
       <c r="AA7">
-        <v>-0.82</v>
+        <v>-137.24</v>
       </c>
       <c r="AB7">
-        <v>118.75</v>
+        <v>565.52</v>
       </c>
       <c r="AC7">
-        <v>360</v>
+        <v>564.29</v>
       </c>
       <c r="AD7">
-        <v>9.1</v>
+        <v>33.12</v>
       </c>
       <c r="AE7">
-        <v>225</v>
+        <v>771.88</v>
       </c>
       <c r="AF7">
-        <v>144.44</v>
+        <v>-3.03</v>
       </c>
       <c r="AG7">
-        <v>-80</v>
+        <v>-21.43</v>
       </c>
       <c r="AH7" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AI7" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="AJ7" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="AK7">
-        <v>58.68244157508708</v>
+        <v>64.57999894664799</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1503,109 +1710,109 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>94.45750097924011</v>
+        <v>92.69108841141247</v>
       </c>
       <c r="C8">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="D8">
-        <v>41.44</v>
+        <v>102.97</v>
       </c>
       <c r="E8">
-        <v>4.88</v>
+        <v>2.74</v>
       </c>
       <c r="F8">
-        <v>0.1760766073324834</v>
+        <v>0.0896920606824768</v>
       </c>
       <c r="G8">
-        <v>3.56</v>
+        <v>2.59</v>
       </c>
       <c r="H8">
-        <v>-0.4057809875123228</v>
+        <v>-0.04732006421696688</v>
       </c>
       <c r="I8">
-        <v>38.60999908447265</v>
+        <v>104.2653991699219</v>
       </c>
       <c r="J8">
-        <v>38.23499946594238</v>
+        <v>107.4289127349853</v>
       </c>
       <c r="K8">
-        <v>31.47219974517822</v>
+        <v>102.0127426147461</v>
       </c>
       <c r="L8">
-        <v>19.76604994773865</v>
+        <v>92.29032638549805</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="N8">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>6.58</v>
+        <v>45.29</v>
       </c>
       <c r="Y8">
-        <v>41.99</v>
+        <v>122.83</v>
       </c>
       <c r="Z8">
-        <v>3.06</v>
+        <v>27.45</v>
       </c>
       <c r="AA8">
-        <v>12.3</v>
+        <v>166.14</v>
       </c>
       <c r="AB8">
-        <v>162</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="AC8">
-        <v>337.5</v>
+        <v>456.49</v>
       </c>
       <c r="AD8">
-        <v>25.93</v>
+        <v>15.94</v>
       </c>
       <c r="AE8">
-        <v>570.59</v>
+        <v>44.36</v>
       </c>
       <c r="AF8">
-        <v>132.69</v>
+        <v>62.9</v>
       </c>
       <c r="AG8">
-        <v>-8.33</v>
+        <v>136.64</v>
       </c>
       <c r="AH8" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AI8" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="AJ8" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="AK8">
-        <v>56.55935430839685</v>
+        <v>63.63640814287825</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1613,43 +1820,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>94.86878182530356</v>
+        <v>92.02183867558999</v>
       </c>
       <c r="C9">
-        <v>428</v>
+        <v>1205</v>
       </c>
       <c r="D9">
-        <v>220.84</v>
+        <v>14.52</v>
       </c>
       <c r="E9">
-        <v>6.07</v>
+        <v>2.96</v>
       </c>
       <c r="F9">
-        <v>0.9521179507608353</v>
+        <v>0.3181359333603272</v>
       </c>
       <c r="G9">
-        <v>4.6</v>
+        <v>5.68</v>
       </c>
       <c r="H9">
-        <v>0.5819072033687359</v>
+        <v>4.020869811468319</v>
       </c>
       <c r="I9">
-        <v>204.8239959716797</v>
+        <v>14.58930511474609</v>
       </c>
       <c r="J9">
-        <v>216.1695007324219</v>
+        <v>15.41015357971191</v>
       </c>
       <c r="K9">
-        <v>207.3647991943359</v>
+        <v>14.15667329788208</v>
       </c>
       <c r="L9">
-        <v>145.5885997009277</v>
+        <v>11.3428107213974</v>
       </c>
       <c r="M9">
         <v>0.95</v>
       </c>
       <c r="N9">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1670,52 +1877,52 @@
         <v>0</v>
       </c>
       <c r="V9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>29.95</v>
+        <v>7.36</v>
       </c>
       <c r="Y9">
-        <v>251.86</v>
+        <v>18.17</v>
       </c>
       <c r="Z9">
-        <v>24.27</v>
+        <v>1.03</v>
       </c>
       <c r="AA9">
-        <v>-171.22</v>
+        <v>-99.44</v>
       </c>
       <c r="AB9">
-        <v>216.48</v>
+        <v>402.23</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>834.49</v>
       </c>
       <c r="AD9">
-        <v>20.01</v>
+        <v>36.78</v>
       </c>
       <c r="AE9">
-        <v>61.33</v>
+        <v>977.78</v>
       </c>
       <c r="AF9">
-        <v>-7.41</v>
+        <v>200</v>
       </c>
       <c r="AG9">
-        <v>636.36</v>
+        <v>-71.09999999999999</v>
       </c>
       <c r="AH9" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="AI9" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="AJ9" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="AK9">
-        <v>56.55684658843503</v>
+        <v>63.02560137150422</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1723,49 +1930,49 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>92.8123775949863</v>
+        <v>91.77527298344488</v>
       </c>
       <c r="C10">
-        <v>2494</v>
+        <v>538</v>
       </c>
       <c r="D10">
-        <v>92.02</v>
+        <v>659.27</v>
       </c>
       <c r="E10">
-        <v>3.16</v>
+        <v>3.39</v>
       </c>
       <c r="F10">
-        <v>-0.9455965949337053</v>
+        <v>0.7646398663215809</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="H10">
-        <v>-0.9376130902944316</v>
+        <v>-0.4027929659758754</v>
       </c>
       <c r="I10">
-        <v>85.65318756103515</v>
+        <v>657.1648803710938</v>
       </c>
       <c r="J10">
-        <v>79.43473320007324</v>
+        <v>632.7115844726562</v>
       </c>
       <c r="K10">
-        <v>70.46390335083008</v>
+        <v>587.1530322265625</v>
       </c>
       <c r="L10">
-        <v>47.82879693984985</v>
+        <v>487.9113529968262</v>
       </c>
       <c r="M10">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1774,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>0.5555555555555555</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1786,46 +1993,46 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>11.14</v>
+        <v>344.82</v>
       </c>
       <c r="Y10">
-        <v>92.40000000000001</v>
+        <v>703.15</v>
       </c>
       <c r="Z10">
-        <v>1.84</v>
+        <v>170.08</v>
       </c>
       <c r="AA10">
-        <v>25.06</v>
+        <v>10.89</v>
       </c>
       <c r="AB10">
-        <v>65.36</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>1038.46</v>
+        <v>1100</v>
       </c>
       <c r="AD10">
-        <v>4.78</v>
+        <v>2.34</v>
       </c>
       <c r="AE10">
-        <v>-10.95</v>
+        <v>-42.86</v>
       </c>
       <c r="AF10">
-        <v>1857.14</v>
+        <v>-72.56999999999999</v>
       </c>
       <c r="AG10">
-        <v>153.85</v>
+        <v>7557.14</v>
       </c>
       <c r="AH10" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="AI10" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AJ10" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="AK10">
-        <v>56.49366927511137</v>
+        <v>62.5530656769778</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1833,109 +2040,109 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>93.77203290246769</v>
+        <v>95.4033110250088</v>
       </c>
       <c r="C11">
-        <v>1538</v>
+        <v>277</v>
       </c>
       <c r="D11">
-        <v>164.34</v>
+        <v>127.09</v>
       </c>
       <c r="E11">
-        <v>3.46</v>
+        <v>2.36</v>
       </c>
       <c r="F11">
-        <v>-0.7499559201198353</v>
+        <v>-0.3048928103065383</v>
       </c>
       <c r="G11">
-        <v>3.23</v>
+        <v>2.39</v>
       </c>
       <c r="H11">
-        <v>-0.7191820480803512</v>
+        <v>-0.310633324779121</v>
       </c>
       <c r="I11">
-        <v>156.8968719482422</v>
+        <v>128.3219833374023</v>
       </c>
       <c r="J11">
-        <v>164.5615440368652</v>
+        <v>129.389644241333</v>
       </c>
       <c r="K11">
-        <v>149.4045245361328</v>
+        <v>119.3619244384766</v>
       </c>
       <c r="L11">
-        <v>99.99583562850952</v>
+        <v>93.57516481399536</v>
       </c>
       <c r="M11">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="N11">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11">
         <v>3</v>
       </c>
       <c r="T11">
-        <v>6.111111111111111</v>
+        <v>20.55555555555555</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>27.15</v>
+        <v>52.96</v>
       </c>
       <c r="Y11">
-        <v>176.98</v>
+        <v>134.78</v>
       </c>
       <c r="Z11">
-        <v>10.75</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AA11">
-        <v>-3.21</v>
+        <v>40.78</v>
       </c>
       <c r="AB11">
-        <v>188.76</v>
+        <v>231.53</v>
       </c>
       <c r="AC11">
-        <v>254.92</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AD11">
-        <v>7.25</v>
+        <v>15.41</v>
       </c>
       <c r="AE11">
-        <v>175.58</v>
+        <v>6.59</v>
       </c>
       <c r="AF11">
-        <v>292.04</v>
+        <v>-26.32</v>
       </c>
       <c r="AG11">
-        <v>70.73</v>
+        <v>118.58</v>
       </c>
       <c r="AH11" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AI11" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="AJ11" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="AK11">
-        <v>56.43904095282988</v>
+        <v>60.3600827043039</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1943,43 +2150,43 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>91.8331374853114</v>
+        <v>90.91229306093696</v>
       </c>
       <c r="C12">
-        <v>2860</v>
+        <v>2749</v>
       </c>
       <c r="D12">
-        <v>80.23</v>
+        <v>242.33</v>
       </c>
       <c r="E12">
-        <v>2.59</v>
+        <v>1.25</v>
       </c>
       <c r="F12">
-        <v>-1.317313877080059</v>
+        <v>-1.457495986090239</v>
       </c>
       <c r="G12">
-        <v>2.88</v>
+        <v>1.57</v>
       </c>
       <c r="H12">
-        <v>-1.051577112319169</v>
+        <v>-1.390217693083954</v>
       </c>
       <c r="I12">
-        <v>80.58400115966796</v>
+        <v>243.4980010986328</v>
       </c>
       <c r="J12">
-        <v>76.36900024414062</v>
+        <v>246.7349998474121</v>
       </c>
       <c r="K12">
-        <v>65.74760009765625</v>
+        <v>227.2972009277344</v>
       </c>
       <c r="L12">
-        <v>41.96060012817383</v>
+        <v>190.4589003753662</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="N12">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1988,64 +2195,64 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T12">
-        <v>1.111111111111111</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>19.03</v>
+        <v>130.82</v>
       </c>
       <c r="Y12">
-        <v>85.65000000000001</v>
+        <v>260</v>
       </c>
       <c r="Z12">
-        <v>1.2</v>
+        <v>9.15</v>
       </c>
       <c r="AA12">
-        <v>14.64</v>
+        <v>-8.52</v>
       </c>
       <c r="AB12">
-        <v>23.08</v>
+        <v>71.72</v>
       </c>
       <c r="AC12">
-        <v>816.67</v>
+        <v>616</v>
       </c>
       <c r="AD12">
-        <v>4.71</v>
+        <v>7.82</v>
       </c>
       <c r="AE12">
-        <v>44.94</v>
+        <v>-35.38</v>
       </c>
       <c r="AF12">
-        <v>58.93</v>
+        <v>1529.41</v>
       </c>
       <c r="AG12">
-        <v>411.11</v>
+        <v>-32</v>
       </c>
       <c r="AH12" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="AI12" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="AJ12" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AK12">
-        <v>52.74589698016101</v>
+        <v>59.90505746970587</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2053,43 +2260,46 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>98.04151978065021</v>
+        <v>94.8573441352589</v>
       </c>
       <c r="C13">
-        <v>1025</v>
+        <v>744</v>
       </c>
       <c r="D13">
-        <v>36.45</v>
+        <v>13.48</v>
       </c>
       <c r="E13">
-        <v>7.57</v>
+        <v>3.07</v>
       </c>
       <c r="F13">
-        <v>1.930321324830186</v>
+        <v>0.4323578696992523</v>
       </c>
       <c r="G13">
-        <v>5.37</v>
+        <v>2.93</v>
       </c>
       <c r="H13">
-        <v>1.313176344694136</v>
+        <v>0.4003124787386961</v>
       </c>
       <c r="I13">
-        <v>34.57749786376953</v>
+        <v>13.25399990081787</v>
       </c>
       <c r="J13">
-        <v>30.66518507003784</v>
+        <v>12.56100001335144</v>
       </c>
       <c r="K13">
-        <v>29.44925491333008</v>
+        <v>11.11240007400513</v>
       </c>
       <c r="L13">
-        <v>20.79182344198227</v>
+        <v>10.51180002689362</v>
       </c>
       <c r="M13">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>1.17</v>
+        <v>1.19</v>
+      </c>
+      <c r="O13" t="s">
+        <v>14</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2101,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -2113,49 +2323,49 @@
         <v>1</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>3.62</v>
+        <v>5.85</v>
       </c>
       <c r="Y13">
-        <v>37.86</v>
+        <v>14.07</v>
       </c>
       <c r="Z13">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="AA13">
-        <v>2.26</v>
+        <v>-34.89</v>
       </c>
       <c r="AB13">
-        <v>138.52</v>
+        <v>122.62</v>
       </c>
       <c r="AC13">
-        <v>526.3200000000001</v>
+        <v>600</v>
       </c>
       <c r="AD13">
-        <v>7.13</v>
+        <v>17.55</v>
       </c>
       <c r="AE13">
-        <v>6.58</v>
+        <v>25</v>
       </c>
       <c r="AF13">
-        <v>183.52</v>
+        <v>166.67</v>
       </c>
       <c r="AG13">
-        <v>-378.95</v>
+        <v>250</v>
       </c>
       <c r="AH13" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="AI13" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="AJ13" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="AK13">
-        <v>46.32519146708425</v>
+        <v>59.27920619888985</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2163,43 +2373,43 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>94.39874657265962</v>
+        <v>97.37583656216978</v>
       </c>
       <c r="C14">
-        <v>1283</v>
+        <v>93</v>
       </c>
       <c r="D14">
-        <v>46.37</v>
+        <v>34.38</v>
       </c>
       <c r="E14">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="F14">
-        <v>0.05869220244416153</v>
+        <v>0.5673474308270735</v>
       </c>
       <c r="G14">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="H14">
-        <v>-0.2158409508044271</v>
+        <v>0.6241287502165273</v>
       </c>
       <c r="I14">
-        <v>46.05999984741211</v>
+        <v>34.90226287841797</v>
       </c>
       <c r="J14">
-        <v>41.69100017547608</v>
+        <v>35.35030136108399</v>
       </c>
       <c r="K14">
-        <v>38.0031999206543</v>
+        <v>33.44391078948975</v>
       </c>
       <c r="L14">
-        <v>23.90030004024506</v>
+        <v>24.10493824958801</v>
       </c>
       <c r="M14">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="N14">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2220,52 +2430,52 @@
         <v>0</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>7.17</v>
+        <v>11.37</v>
       </c>
       <c r="Y14">
-        <v>50.89</v>
+        <v>37.66</v>
       </c>
       <c r="Z14">
-        <v>2.25</v>
+        <v>19.93</v>
       </c>
       <c r="AA14">
-        <v>0.97</v>
+        <v>-0.38</v>
       </c>
       <c r="AB14">
-        <v>2800</v>
+        <v>119.22</v>
       </c>
       <c r="AC14">
-        <v>333.33</v>
+        <v>559.26</v>
       </c>
       <c r="AD14">
-        <v>9.48</v>
+        <v>9.31</v>
       </c>
       <c r="AE14">
-        <v>-7.14</v>
+        <v>226.32</v>
       </c>
       <c r="AF14">
-        <v>33.33</v>
+        <v>15.15</v>
       </c>
       <c r="AG14">
-        <v>250</v>
+        <v>222.22</v>
       </c>
       <c r="AH14" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AI14" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="AJ14" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="AK14">
-        <v>45.83691169137548</v>
+        <v>57.09294728248759</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2273,49 +2483,49 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>97.04269486878182</v>
+        <v>99.38358576963719</v>
       </c>
       <c r="C15">
-        <v>1208</v>
+        <v>2669</v>
       </c>
       <c r="D15">
-        <v>45.79</v>
+        <v>29.25</v>
       </c>
       <c r="E15">
-        <v>4.62</v>
+        <v>2.22</v>
       </c>
       <c r="F15">
-        <v>0.006521355827129445</v>
+        <v>-0.4502661838288065</v>
       </c>
       <c r="G15">
-        <v>4.26</v>
+        <v>1.8</v>
       </c>
       <c r="H15">
-        <v>0.2590091409653129</v>
+        <v>-1.087407443437477</v>
       </c>
       <c r="I15">
-        <v>42.44000015258789</v>
+        <v>28.8710391998291</v>
       </c>
       <c r="J15">
-        <v>39.18150005340576</v>
+        <v>29.90733032226563</v>
       </c>
       <c r="K15">
-        <v>35.27480003356933</v>
+        <v>28.74483104705811</v>
       </c>
       <c r="L15">
-        <v>24.05395002841949</v>
+        <v>19.76659554061875</v>
       </c>
       <c r="M15">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="N15">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2324,58 +2534,58 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
       </c>
       <c r="X15">
-        <v>5.61</v>
+        <v>5.14</v>
       </c>
       <c r="Y15">
-        <v>46.5</v>
+        <v>31.59</v>
       </c>
       <c r="Z15">
-        <v>1.85</v>
+        <v>3.38</v>
       </c>
       <c r="AA15">
-        <v>-21.39</v>
+        <v>1.62</v>
       </c>
       <c r="AB15">
-        <v>229.55</v>
+        <v>200</v>
       </c>
       <c r="AC15">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="AD15">
-        <v>8.6</v>
+        <v>0.66</v>
       </c>
       <c r="AE15">
-        <v>23.53</v>
-      </c>
-      <c r="AF15">
-        <v>585.71</v>
+        <v>116.67</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>108</v>
       </c>
       <c r="AG15">
-        <v>41.67</v>
+        <v>100</v>
       </c>
       <c r="AH15" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="AI15" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="AJ15" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="AK15">
-        <v>45.07921796025373</v>
+        <v>56.91999945656529</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2383,43 +2593,43 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>94.20289855072464</v>
+        <v>91.88094399436422</v>
       </c>
       <c r="C16">
-        <v>349</v>
+        <v>2233</v>
       </c>
       <c r="D16">
-        <v>4.54</v>
+        <v>57.75</v>
       </c>
       <c r="E16">
-        <v>4.48</v>
+        <v>2.03</v>
       </c>
       <c r="F16">
-        <v>-0.08477762575267642</v>
+        <v>-0.6475586193233143</v>
       </c>
       <c r="G16">
-        <v>4.25</v>
+        <v>2.29</v>
       </c>
       <c r="H16">
-        <v>0.2495121391299183</v>
+        <v>-0.4422899550601983</v>
       </c>
       <c r="I16">
-        <v>4.251445865631103</v>
+        <v>57.34799957275391</v>
       </c>
       <c r="J16">
-        <v>4.236204278469086</v>
+        <v>58.32599983215332</v>
       </c>
       <c r="K16">
-        <v>4.256594471931457</v>
+        <v>51.43320007324219</v>
       </c>
       <c r="L16">
-        <v>2.653665160536766</v>
+        <v>46.49634996414184</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2440,52 +2650,52 @@
         <v>0</v>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>0.6899999999999999</v>
+        <v>26.77</v>
       </c>
       <c r="Y16">
-        <v>4.9</v>
+        <v>61.08</v>
       </c>
       <c r="Z16">
-        <v>5.56</v>
+        <v>2.17</v>
       </c>
       <c r="AA16">
-        <v>881.49</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="AB16">
-        <v>364.14</v>
+        <v>352.63</v>
       </c>
       <c r="AC16">
-        <v>342.46</v>
+        <v>352.63</v>
       </c>
       <c r="AD16">
-        <v>37.16</v>
+        <v>7.82</v>
       </c>
       <c r="AE16">
-        <v>206.45</v>
+        <v>21.13</v>
       </c>
       <c r="AF16">
-        <v>181.67</v>
+        <v>82.05</v>
       </c>
       <c r="AG16">
-        <v>128.09</v>
+        <v>105.26</v>
       </c>
       <c r="AH16" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AI16" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="AJ16" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="AK16">
-        <v>42.0582377103549</v>
+        <v>55.54015625348797</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2493,58 +2703,58 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>93.90912651782217</v>
+        <v>92.74392391687213</v>
       </c>
       <c r="C17">
-        <v>816</v>
+        <v>1939</v>
       </c>
       <c r="D17">
-        <v>31.51</v>
+        <v>31.92</v>
       </c>
       <c r="E17">
-        <v>5.33</v>
+        <v>2.49</v>
       </c>
       <c r="F17">
-        <v>0.4695376195532888</v>
+        <v>-0.1699032491787171</v>
       </c>
       <c r="G17">
-        <v>3.93</v>
+        <v>2.53</v>
       </c>
       <c r="H17">
-        <v>-0.05439191960271512</v>
+        <v>-0.1263140423856133</v>
       </c>
       <c r="I17">
-        <v>29.03400039672852</v>
+        <v>30.95878791809082</v>
       </c>
       <c r="J17">
-        <v>27.17150001525879</v>
+        <v>31.76325283050537</v>
       </c>
       <c r="K17">
-        <v>25.4034001159668</v>
+        <v>31.42869636535644</v>
       </c>
       <c r="L17">
-        <v>16.43250003576279</v>
+        <v>27.00407567024231</v>
       </c>
       <c r="M17">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="N17">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -2556,46 +2766,46 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>3.72</v>
+        <v>15.89</v>
       </c>
       <c r="Y17">
-        <v>31.67</v>
+        <v>34.13</v>
       </c>
       <c r="Z17">
-        <v>2.68</v>
+        <v>20.55</v>
       </c>
       <c r="AA17">
-        <v>0.06</v>
+        <v>3.36</v>
       </c>
       <c r="AB17">
-        <v>150</v>
+        <v>142.5</v>
       </c>
       <c r="AC17">
-        <v>382.35</v>
+        <v>186.99</v>
       </c>
       <c r="AD17">
-        <v>2.96</v>
+        <v>4.28</v>
       </c>
       <c r="AE17">
-        <v>-21.31</v>
+        <v>148.07</v>
       </c>
       <c r="AF17">
-        <v>198.39</v>
+        <v>-1.61</v>
       </c>
       <c r="AG17">
-        <v>-264.71</v>
+        <v>135.64</v>
       </c>
       <c r="AH17" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AI17" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AJ17" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="AK17">
-        <v>41.84902344216797</v>
+        <v>55.49881384791733</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2603,46 +2813,43 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>93.49784567175871</v>
+        <v>93.11377245508982</v>
       </c>
       <c r="C18">
-        <v>1341</v>
+        <v>3252.5</v>
       </c>
       <c r="D18">
-        <v>35.98</v>
+        <v>97.06</v>
       </c>
       <c r="E18">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="F18">
-        <v>-1.245578962981639</v>
+        <v>0.8788618026605061</v>
       </c>
       <c r="G18">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="H18">
-        <v>-1.602403218772068</v>
+        <v>-0.1131483793575053</v>
       </c>
       <c r="I18">
-        <v>34.50599975585938</v>
+        <v>98.85677642822266</v>
       </c>
       <c r="J18">
-        <v>31.99100008010864</v>
+        <v>103.3755977630615</v>
       </c>
       <c r="K18">
-        <v>30.52040004730225</v>
+        <v>92.79042587280273</v>
       </c>
       <c r="L18">
-        <v>22.42730002880096</v>
+        <v>78.75841234207154</v>
       </c>
       <c r="M18">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="N18">
-        <v>1.13</v>
-      </c>
-      <c r="O18" t="s">
-        <v>14</v>
+        <v>1.07</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2654,61 +2861,61 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>4.31</v>
+        <v>46.82</v>
       </c>
       <c r="Y18">
-        <v>36.56</v>
+        <v>112.72</v>
       </c>
       <c r="Z18">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="AA18">
-        <v>-5.86</v>
+        <v>48.8</v>
       </c>
       <c r="AB18">
-        <v>187.83</v>
+        <v>209.2</v>
       </c>
       <c r="AC18">
-        <v>214.67</v>
+        <v>377.78</v>
       </c>
       <c r="AD18">
-        <v>8.630000000000001</v>
+        <v>4.03</v>
       </c>
       <c r="AE18">
-        <v>-6.64</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="AF18">
-        <v>189.74</v>
+        <v>35.71</v>
       </c>
       <c r="AG18">
-        <v>142.39</v>
+        <v>288.89</v>
       </c>
       <c r="AH18" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AI18" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="AJ18" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="AK18">
-        <v>39.39453887517589</v>
+        <v>55.0053426711583</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2716,43 +2923,43 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>93.45867606737171</v>
+        <v>92.60302923564635</v>
       </c>
       <c r="C19">
-        <v>1178</v>
+        <v>2679</v>
       </c>
       <c r="D19">
-        <v>161.1</v>
+        <v>7.25</v>
       </c>
       <c r="E19">
-        <v>7.13</v>
+        <v>2.01</v>
       </c>
       <c r="F19">
-        <v>1.643381668436509</v>
+        <v>-0.6683262441122099</v>
       </c>
       <c r="G19">
-        <v>4.77</v>
+        <v>1.99</v>
       </c>
       <c r="H19">
-        <v>0.7433562345704474</v>
+        <v>-0.8372598459034301</v>
       </c>
       <c r="I19">
-        <v>144.5380004882813</v>
+        <v>7.27736930847168</v>
       </c>
       <c r="J19">
-        <v>169.3945007324219</v>
+        <v>7.407938814163208</v>
       </c>
       <c r="K19">
-        <v>157.3618002319336</v>
+        <v>6.952611570358276</v>
       </c>
       <c r="L19">
-        <v>105.7135999107361</v>
+        <v>5.840216476917266</v>
       </c>
       <c r="M19">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="N19">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2761,64 +2968,64 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="T19">
-        <v>4.444444444444444</v>
+        <v>0</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>18.65</v>
+        <v>3.6</v>
       </c>
       <c r="Y19">
-        <v>212.4</v>
+        <v>7.88</v>
       </c>
       <c r="Z19">
-        <v>34.19</v>
+        <v>7.69</v>
       </c>
       <c r="AA19">
-        <v>11.95</v>
+        <v>-22500</v>
       </c>
       <c r="AB19">
-        <v>65.04000000000001</v>
+        <v>800</v>
       </c>
       <c r="AC19">
-        <v>125.64</v>
+        <v>260</v>
       </c>
       <c r="AD19">
-        <v>0.97</v>
+        <v>5.35</v>
       </c>
       <c r="AE19">
-        <v>17.65</v>
+        <v>63.64</v>
       </c>
       <c r="AF19">
-        <v>144.74</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>51.28</v>
+        <v>120</v>
       </c>
       <c r="AH19" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="AI19" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="AJ19" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="AK19">
-        <v>38.59081010226798</v>
+        <v>54.74032187909658</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2826,43 +3033,43 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>93.55660007833922</v>
+        <v>92.05706234589644</v>
       </c>
       <c r="C20">
-        <v>2200</v>
+        <v>3132</v>
       </c>
       <c r="D20">
-        <v>388.99</v>
+        <v>48.07</v>
       </c>
       <c r="E20">
-        <v>2.74</v>
+        <v>4.04</v>
       </c>
       <c r="F20">
-        <v>-1.219493539673123</v>
+        <v>1.439587671960685</v>
       </c>
       <c r="G20">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="H20">
-        <v>-0.9661040958006158</v>
+        <v>0.7426197174694965</v>
       </c>
       <c r="I20">
-        <v>375.3427062988281</v>
+        <v>47.53913269042969</v>
       </c>
       <c r="J20">
-        <v>367.6892807006836</v>
+        <v>49.14722194671631</v>
       </c>
       <c r="K20">
-        <v>338.5775677490234</v>
+        <v>42.52680076599121</v>
       </c>
       <c r="L20">
-        <v>252.6840493774414</v>
+        <v>38.6099893283844</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="N20">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2874,61 +3081,61 @@
         <v>1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <v>1.111111111111111</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
       </c>
       <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="b">
         <v>1</v>
       </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
       <c r="X20">
-        <v>54.11</v>
+        <v>24.72</v>
       </c>
       <c r="Y20">
-        <v>403.32</v>
+        <v>52.86</v>
       </c>
       <c r="Z20">
-        <v>6.88</v>
+        <v>1.33</v>
       </c>
       <c r="AA20">
-        <v>5.44</v>
+        <v>-80000</v>
       </c>
       <c r="AB20">
-        <v>44.19</v>
+        <v>1042.86</v>
       </c>
       <c r="AC20">
-        <v>271.86</v>
+        <v>156.52</v>
       </c>
       <c r="AD20">
-        <v>7.05</v>
+        <v>8.5</v>
       </c>
       <c r="AE20">
-        <v>6.47</v>
+        <v>31.11</v>
       </c>
       <c r="AF20">
-        <v>104.41</v>
+        <v>36.36</v>
       </c>
       <c r="AG20">
-        <v>70.84999999999999</v>
+        <v>43.48</v>
       </c>
       <c r="AH20" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AI20" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="AJ20" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="AK20">
-        <v>38.07055461160051</v>
+        <v>53.6379535436348</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2936,43 +3143,43 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>95.24089306698002</v>
+        <v>94.01197604790418</v>
       </c>
       <c r="C21">
-        <v>51</v>
+        <v>258</v>
       </c>
       <c r="D21">
-        <v>35.6</v>
+        <v>62.54</v>
       </c>
       <c r="E21">
-        <v>4.41</v>
+        <v>2.3</v>
       </c>
       <c r="F21">
-        <v>-0.1304271165425796</v>
+        <v>-0.3671956846732249</v>
       </c>
       <c r="G21">
-        <v>3.87</v>
+        <v>2.81</v>
       </c>
       <c r="H21">
-        <v>-0.111373930615084</v>
+        <v>0.2423245224014033</v>
       </c>
       <c r="I21">
-        <v>33.30222320556641</v>
+        <v>61.79800033569336</v>
       </c>
       <c r="J21">
-        <v>33.12976217269897</v>
+        <v>60.73350028991699</v>
       </c>
       <c r="K21">
-        <v>30.00677501678467</v>
+        <v>52.28820014953613</v>
       </c>
       <c r="L21">
-        <v>19.08649142742157</v>
+        <v>43.40959995269775</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N21">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2984,61 +3191,61 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>4.58</v>
+        <v>29.03</v>
       </c>
       <c r="Y21">
-        <v>37.15</v>
+        <v>65.47</v>
       </c>
       <c r="Z21">
-        <v>36.12</v>
+        <v>20.17</v>
       </c>
       <c r="AA21">
-        <v>-0.04</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="AB21">
-        <v>180.39</v>
+        <v>122.54</v>
       </c>
       <c r="AC21">
-        <v>247.06</v>
+        <v>242.86</v>
       </c>
       <c r="AD21">
-        <v>4.6</v>
+        <v>7.49</v>
       </c>
       <c r="AE21">
-        <v>127.27</v>
+        <v>67.44</v>
       </c>
       <c r="AF21">
-        <v>633.33</v>
+        <v>95.45</v>
       </c>
       <c r="AG21">
-        <v>108.82</v>
+        <v>4.76</v>
       </c>
       <c r="AH21" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="AI21" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="AJ21" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="AK21">
-        <v>35.89295989012356</v>
+        <v>53.25713174902352</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3046,58 +3253,58 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <v>97.35605170387778</v>
+        <v>93.46600915815428</v>
       </c>
       <c r="C22">
-        <v>2097</v>
+        <v>636</v>
       </c>
       <c r="D22">
-        <v>63.51</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="E22">
-        <v>6.18</v>
+        <v>2.68</v>
       </c>
       <c r="F22">
-        <v>1.023852864859254</v>
+        <v>0.02738918631579021</v>
       </c>
       <c r="G22">
-        <v>4.59</v>
+        <v>2.04</v>
       </c>
       <c r="H22">
-        <v>0.5724102015333413</v>
+        <v>-0.7714315307628914</v>
       </c>
       <c r="I22">
-        <v>54.2</v>
+        <v>71.25200042724609</v>
       </c>
       <c r="J22">
-        <v>52.57099952697754</v>
+        <v>69.56699981689454</v>
       </c>
       <c r="K22">
-        <v>53.15359985351562</v>
+        <v>61.53959991455078</v>
       </c>
       <c r="L22">
-        <v>32.99012495994568</v>
+        <v>50.44345001220703</v>
       </c>
       <c r="M22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N22">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
       <c r="T22">
-        <v>1.111111111111111</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
@@ -3106,49 +3313,49 @@
         <v>1</v>
       </c>
       <c r="W22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>7.5</v>
+        <v>34.42</v>
       </c>
       <c r="Y22">
-        <v>65.73999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="Z22">
-        <v>1.42</v>
+        <v>10.64</v>
       </c>
       <c r="AA22">
-        <v>0.25</v>
+        <v>104.94</v>
       </c>
       <c r="AB22">
-        <v>15.79</v>
+        <v>144.41</v>
       </c>
       <c r="AC22">
-        <v>266.67</v>
+        <v>152.1</v>
       </c>
       <c r="AD22">
-        <v>11.41</v>
+        <v>11.1</v>
       </c>
       <c r="AE22">
-        <v>-8.33</v>
+        <v>25</v>
       </c>
       <c r="AF22">
-        <v>71.43000000000001</v>
+        <v>185.71</v>
       </c>
       <c r="AG22">
-        <v>133.33</v>
+        <v>-29.41</v>
       </c>
       <c r="AH22" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="AI22" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="AJ22" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="AK22">
-        <v>35.76454763885821</v>
+        <v>52.78092064432911</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3156,43 +3363,43 @@
         <v>58</v>
       </c>
       <c r="B23">
-        <v>97.47356051703878</v>
+        <v>97.19971821063756</v>
       </c>
       <c r="C23">
-        <v>1132</v>
+        <v>2378</v>
       </c>
       <c r="D23">
-        <v>33.1</v>
+        <v>46.78</v>
       </c>
       <c r="E23">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="F23">
-        <v>-0.9064684599709312</v>
+        <v>0.6919531795604462</v>
       </c>
       <c r="G23">
-        <v>4.59</v>
+        <v>2.52</v>
       </c>
       <c r="H23">
-        <v>0.5724102015333413</v>
+        <v>-0.1394797054137207</v>
       </c>
       <c r="I23">
-        <v>31.04999961853027</v>
+        <v>46.83399963378906</v>
       </c>
       <c r="J23">
-        <v>32.90999975204468</v>
+        <v>48.21049976348877</v>
       </c>
       <c r="K23">
-        <v>30.3951997756958</v>
+        <v>41.44819984436035</v>
       </c>
       <c r="L23">
-        <v>21.4241499042511</v>
+        <v>33.18694994926452</v>
       </c>
       <c r="M23">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="N23">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3213,52 +3420,52 @@
         <v>0</v>
       </c>
       <c r="V23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="b">
         <v>0</v>
       </c>
       <c r="X23">
-        <v>4.29</v>
+        <v>16.08</v>
       </c>
       <c r="Y23">
-        <v>38.36</v>
+        <v>52.33</v>
       </c>
       <c r="Z23">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AA23">
-        <v>2.91</v>
+        <v>15.38</v>
       </c>
       <c r="AB23">
-        <v>128.05</v>
+        <v>550</v>
       </c>
       <c r="AC23">
-        <v>155.56</v>
+        <v>219.05</v>
       </c>
       <c r="AD23">
-        <v>11.97</v>
+        <v>11.76</v>
       </c>
       <c r="AE23">
-        <v>-1.46</v>
+        <v>-1.57</v>
       </c>
       <c r="AF23">
-        <v>95.70999999999999</v>
+        <v>20.95</v>
       </c>
       <c r="AG23">
-        <v>128.81</v>
+        <v>200</v>
       </c>
       <c r="AH23" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="AI23" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="AJ23" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="AK23">
-        <v>28.50169677264495</v>
+        <v>52.51132798645524</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3266,43 +3473,43 @@
         <v>59</v>
       </c>
       <c r="B24">
-        <v>90.87348217783</v>
+        <v>95.12152166255724</v>
       </c>
       <c r="C24">
-        <v>623</v>
+        <v>120</v>
       </c>
       <c r="D24">
-        <v>14.61</v>
+        <v>11.3</v>
       </c>
       <c r="E24">
-        <v>4.09</v>
+        <v>3.04</v>
       </c>
       <c r="F24">
-        <v>-0.339110503010708</v>
+        <v>0.4012064325159093</v>
       </c>
       <c r="G24">
-        <v>3.53</v>
+        <v>2.82</v>
       </c>
       <c r="H24">
-        <v>-0.4342719930185074</v>
+        <v>0.2554901854295107</v>
       </c>
       <c r="I24">
-        <v>14.54286785125732</v>
+        <v>11.33168411254883</v>
       </c>
       <c r="J24">
-        <v>13.22595634460449</v>
+        <v>11.6942195892334</v>
       </c>
       <c r="K24">
-        <v>12.08231407165527</v>
+        <v>10.93369068145752</v>
       </c>
       <c r="L24">
-        <v>8.435612926483154</v>
+        <v>8.550664181709289</v>
       </c>
       <c r="M24">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="N24">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -3323,52 +3530,52 @@
         <v>0</v>
       </c>
       <c r="V24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y24">
-        <v>15.53</v>
+        <v>12.61</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>19.23</v>
       </c>
       <c r="AA24">
-        <v>46.82</v>
+        <v>-4.91</v>
       </c>
       <c r="AB24">
-        <v>15.69</v>
+        <v>120.46</v>
       </c>
       <c r="AC24">
-        <v>205.26</v>
+        <v>308.25</v>
       </c>
       <c r="AD24">
-        <v>9.35</v>
+        <v>2.31</v>
       </c>
       <c r="AE24">
-        <v>9.09</v>
+        <v>142.19</v>
       </c>
       <c r="AF24">
-        <v>-8.33</v>
+        <v>13.42</v>
       </c>
       <c r="AG24">
-        <v>205.26</v>
+        <v>175.82</v>
       </c>
       <c r="AH24" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="AI24" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="AJ24" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="AK24">
-        <v>28.32509834480536</v>
+        <v>52.13477639851438</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3376,43 +3583,43 @@
         <v>60</v>
       </c>
       <c r="B25">
-        <v>92.96905601253427</v>
+        <v>96.67136315604085</v>
       </c>
       <c r="C25">
-        <v>290</v>
+        <v>2034</v>
       </c>
       <c r="D25">
-        <v>157.26</v>
+        <v>81.94</v>
       </c>
       <c r="E25">
-        <v>6.98</v>
+        <v>2.26</v>
       </c>
       <c r="F25">
-        <v>1.545561331029575</v>
+        <v>-0.4087309342510159</v>
       </c>
       <c r="G25">
-        <v>4.79</v>
+        <v>2.37</v>
       </c>
       <c r="H25">
-        <v>0.7623502382412375</v>
+        <v>-0.3369646508353364</v>
       </c>
       <c r="I25">
-        <v>140.4620025634766</v>
+        <v>79.1739990234375</v>
       </c>
       <c r="J25">
-        <v>163.8654998779297</v>
+        <v>77.84799919128417</v>
       </c>
       <c r="K25">
-        <v>151.1835006713867</v>
+        <v>68.71479942321777</v>
       </c>
       <c r="L25">
-        <v>103.6619750022888</v>
+        <v>55.53569986343384</v>
       </c>
       <c r="M25">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>0.93</v>
+        <v>1.15</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -3424,10 +3631,10 @@
         <v>1</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T25">
-        <v>1.111111111111111</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -3436,49 +3643,49 @@
         <v>1</v>
       </c>
       <c r="W25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>20.04</v>
+        <v>29.24</v>
       </c>
       <c r="Y25">
-        <v>208.11</v>
+        <v>82.73</v>
       </c>
       <c r="Z25">
-        <v>32.64</v>
+        <v>3.44</v>
       </c>
       <c r="AA25">
-        <v>11.95</v>
+        <v>19.56</v>
       </c>
       <c r="AB25">
-        <v>65.04000000000001</v>
+        <v>100.76</v>
       </c>
       <c r="AC25">
-        <v>125.64</v>
+        <v>134.21</v>
       </c>
       <c r="AD25">
-        <v>0.97</v>
+        <v>7.65</v>
       </c>
       <c r="AE25">
-        <v>17.65</v>
+        <v>17.11</v>
       </c>
       <c r="AF25">
-        <v>144.74</v>
+        <v>26.67</v>
       </c>
       <c r="AG25">
-        <v>51.28</v>
+        <v>57.89</v>
       </c>
       <c r="AH25" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AI25" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="AJ25" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="AK25">
-        <v>27.68171919317707</v>
+        <v>52.00313968878906</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3486,43 +3693,43 @@
         <v>61</v>
       </c>
       <c r="B26">
-        <v>90.54054054054053</v>
+        <v>93.62451567453328</v>
       </c>
       <c r="C26">
-        <v>1675</v>
+        <v>2073</v>
       </c>
       <c r="D26">
-        <v>331.76</v>
+        <v>93.73</v>
       </c>
       <c r="E26">
-        <v>5.11</v>
+        <v>2.53</v>
       </c>
       <c r="F26">
-        <v>0.3260677913564508</v>
+        <v>-0.1283679996009265</v>
       </c>
       <c r="G26">
-        <v>3.76</v>
+        <v>2.18</v>
       </c>
       <c r="H26">
-        <v>-0.2158409508044271</v>
+        <v>-0.587112248369383</v>
       </c>
       <c r="I26">
-        <v>311.4480041503906</v>
+        <v>93.44400177001953</v>
       </c>
       <c r="J26">
-        <v>328.377001953125</v>
+        <v>90.8120002746582</v>
       </c>
       <c r="K26">
-        <v>285.056198425293</v>
+        <v>81.10059982299805</v>
       </c>
       <c r="L26">
-        <v>203.6288492584229</v>
+        <v>71.77050016403199</v>
       </c>
       <c r="M26">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="N26">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -3534,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U26" t="b">
         <v>0</v>
@@ -3546,49 +3753,49 @@
         <v>1</v>
       </c>
       <c r="W26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>75.5</v>
+        <v>44.59</v>
       </c>
       <c r="Y26">
-        <v>364</v>
+        <v>101.26</v>
       </c>
       <c r="Z26">
-        <v>14.49</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>67.42</v>
+        <v>16</v>
       </c>
       <c r="AB26">
-        <v>17.36</v>
+        <v>2700</v>
       </c>
       <c r="AC26">
-        <v>192.75</v>
+        <v>85</v>
       </c>
       <c r="AD26">
-        <v>8.99</v>
+        <v>2.65</v>
       </c>
       <c r="AE26">
-        <v>8.6</v>
+        <v>4.23</v>
       </c>
       <c r="AF26">
-        <v>78.84999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="AG26">
-        <v>50.72</v>
+        <v>22.5</v>
       </c>
       <c r="AH26" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="AI26" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AJ26" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="AK26">
-        <v>27.61019872730235</v>
+        <v>49.57012761444669</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3596,43 +3803,43 @@
         <v>62</v>
       </c>
       <c r="B27">
-        <v>97.51273012142578</v>
+        <v>90.89468122578373</v>
       </c>
       <c r="C27">
-        <v>336</v>
+        <v>779</v>
       </c>
       <c r="D27">
-        <v>49.65</v>
+        <v>38.74</v>
       </c>
       <c r="E27">
-        <v>8.550000000000001</v>
+        <v>1.92</v>
       </c>
       <c r="F27">
-        <v>2.569414195888829</v>
+        <v>-0.7617805556622395</v>
       </c>
       <c r="G27">
-        <v>8.16</v>
+        <v>1.88</v>
       </c>
       <c r="H27">
-        <v>3.962839856769285</v>
+        <v>-0.9820821392126151</v>
       </c>
       <c r="I27">
-        <v>42.69800033569336</v>
+        <v>38.46199951171875</v>
       </c>
       <c r="J27">
-        <v>50.78800010681152</v>
+        <v>38.42449970245362</v>
       </c>
       <c r="K27">
-        <v>42.13659999847412</v>
+        <v>35.06119964599609</v>
       </c>
       <c r="L27">
-        <v>17.93464997053146</v>
+        <v>29.99977491378784</v>
       </c>
       <c r="M27">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3653,52 +3860,52 @@
         <v>0</v>
       </c>
       <c r="V27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="b">
         <v>1</v>
       </c>
       <c r="X27">
-        <v>4.09</v>
+        <v>20.9</v>
       </c>
       <c r="Y27">
-        <v>64.39</v>
+        <v>40.19</v>
       </c>
       <c r="Z27">
-        <v>2.97</v>
-      </c>
-      <c r="AA27">
-        <v>-3055.56</v>
+        <v>7.35</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>107</v>
       </c>
       <c r="AB27">
-        <v>16.67</v>
+        <v>130.61</v>
       </c>
       <c r="AC27">
-        <v>150</v>
+        <v>217.39</v>
       </c>
       <c r="AD27">
-        <v>1.54</v>
+        <v>2.92</v>
       </c>
       <c r="AE27">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AF27">
-        <v>72.22</v>
+        <v>350</v>
       </c>
       <c r="AG27">
-        <v>-100</v>
+        <v>108.7</v>
       </c>
       <c r="AH27" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AI27" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="AJ27" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="AK27">
-        <v>23.90571157605565</v>
+        <v>49.39084370458065</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3706,43 +3913,43 @@
         <v>63</v>
       </c>
       <c r="B28">
-        <v>92.28358793576184</v>
+        <v>92.21556886227546</v>
       </c>
       <c r="C28">
-        <v>285</v>
+        <v>1745</v>
       </c>
       <c r="D28">
-        <v>6.99</v>
+        <v>126.8</v>
       </c>
       <c r="E28">
-        <v>4.47</v>
+        <v>3.26</v>
       </c>
       <c r="F28">
-        <v>-0.09129898157980586</v>
+        <v>0.6296503051937596</v>
       </c>
       <c r="G28">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="H28">
-        <v>-0.3677929801707436</v>
+        <v>0.4134781417668035</v>
       </c>
       <c r="I28">
-        <v>6.914625263214111</v>
+        <v>125.5940002441406</v>
       </c>
       <c r="J28">
-        <v>6.642556834220886</v>
+        <v>124.8084995269775</v>
       </c>
       <c r="K28">
-        <v>6.181410064697266</v>
+        <v>122.3639996337891</v>
       </c>
       <c r="L28">
-        <v>4.722398525476455</v>
+        <v>106.2020999145508</v>
       </c>
       <c r="M28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3769,46 +3976,46 @@
         <v>1</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>65.16</v>
       </c>
       <c r="Y28">
-        <v>7.17</v>
+        <v>133.48</v>
       </c>
       <c r="Z28">
-        <v>2.62</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>70</v>
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AA28">
+        <v>11.34</v>
       </c>
       <c r="AB28">
-        <v>83.84999999999999</v>
+        <v>140.59</v>
       </c>
       <c r="AC28">
-        <v>117.28</v>
+        <v>213.33</v>
       </c>
       <c r="AD28">
-        <v>3.16</v>
+        <v>15.35</v>
       </c>
       <c r="AE28">
-        <v>-36.36</v>
+        <v>5.94</v>
       </c>
       <c r="AF28">
-        <v>15.79</v>
+        <v>69.44</v>
       </c>
       <c r="AG28">
-        <v>123.46</v>
+        <v>74.55</v>
       </c>
       <c r="AH28" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="AI28" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="AJ28" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="AK28">
-        <v>23.56499295828905</v>
+        <v>49.38962945464035</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3816,43 +4023,43 @@
         <v>64</v>
       </c>
       <c r="B29">
-        <v>94.88836662749706</v>
+        <v>90.84184572032406</v>
       </c>
       <c r="C29">
-        <v>934</v>
+        <v>2663</v>
       </c>
       <c r="D29">
-        <v>7.61</v>
+        <v>319.26</v>
       </c>
       <c r="E29">
-        <v>5.54</v>
+        <v>2.32</v>
       </c>
       <c r="F29">
-        <v>0.6064860919229978</v>
+        <v>-0.3464280598843293</v>
       </c>
       <c r="G29">
-        <v>4.51</v>
+        <v>2.66</v>
       </c>
       <c r="H29">
-        <v>0.4964341868501829</v>
+        <v>0.04483957697978754</v>
       </c>
       <c r="I29">
-        <v>7.046017456054687</v>
+        <v>327.5019958496094</v>
       </c>
       <c r="J29">
-        <v>7.204695916175842</v>
+        <v>342.9264984130859</v>
       </c>
       <c r="K29">
-        <v>6.81860032081604</v>
+        <v>296.8083996582031</v>
       </c>
       <c r="L29">
-        <v>4.964993818998336</v>
+        <v>243.7365497589111</v>
       </c>
       <c r="M29">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="N29">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -3864,61 +4071,61 @@
         <v>0</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U29" t="b">
         <v>0</v>
       </c>
       <c r="V29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="b">
         <v>1</v>
       </c>
       <c r="X29">
-        <v>1.22</v>
+        <v>171.16</v>
       </c>
       <c r="Y29">
-        <v>8.31</v>
+        <v>365.5</v>
       </c>
       <c r="Z29">
-        <v>1.81</v>
+        <v>6.36</v>
       </c>
       <c r="AA29">
-        <v>5.02</v>
+        <v>29.48</v>
       </c>
       <c r="AB29">
-        <v>65.84</v>
+        <v>36.66</v>
       </c>
       <c r="AC29">
-        <v>110.34</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="AD29">
-        <v>0.44</v>
+        <v>6.96</v>
       </c>
       <c r="AE29">
-        <v>133.33</v>
+        <v>27.85</v>
       </c>
       <c r="AF29">
-        <v>55</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG29">
-        <v>31.03</v>
+        <v>-7.19</v>
       </c>
       <c r="AH29" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="AI29" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="AJ29" t="s">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="AK29">
-        <v>22.19710334364394</v>
+        <v>49.32336399122578</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -3926,43 +4133,43 @@
         <v>65</v>
       </c>
       <c r="B30">
-        <v>96.84684684684684</v>
+        <v>94.08242338851707</v>
       </c>
       <c r="C30">
-        <v>672</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>49.18</v>
+        <v>16.28</v>
       </c>
       <c r="E30">
-        <v>5.5</v>
+        <v>2.41</v>
       </c>
       <c r="F30">
-        <v>0.5804006686144818</v>
+        <v>-0.2529737483342992</v>
       </c>
       <c r="G30">
-        <v>4.58</v>
+        <v>2.52</v>
       </c>
       <c r="H30">
-        <v>0.5629131996979467</v>
+        <v>-0.1394797054137207</v>
       </c>
       <c r="I30">
-        <v>45.46399993896485</v>
+        <v>16.0637372970581</v>
       </c>
       <c r="J30">
-        <v>51.05000019073486</v>
+        <v>16.13389272689819</v>
       </c>
       <c r="K30">
-        <v>45.75119987487793</v>
+        <v>14.02580110549927</v>
       </c>
       <c r="L30">
-        <v>26.42599998950958</v>
+        <v>11.58226632118225</v>
       </c>
       <c r="M30">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -3986,49 +4193,49 @@
         <v>1</v>
       </c>
       <c r="W30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>5.14</v>
+        <v>6.87</v>
       </c>
       <c r="Y30">
-        <v>63.88</v>
+        <v>17.03</v>
       </c>
       <c r="Z30">
-        <v>4.1</v>
+        <v>46.58</v>
       </c>
       <c r="AA30">
-        <v>3.88</v>
+        <v>5.35</v>
       </c>
       <c r="AB30">
-        <v>20.83</v>
+        <v>196</v>
       </c>
       <c r="AC30">
-        <v>111.11</v>
+        <v>165.71</v>
       </c>
       <c r="AD30">
-        <v>0.31</v>
+        <v>4.96</v>
       </c>
       <c r="AE30">
-        <v>150</v>
+        <v>228.57</v>
       </c>
       <c r="AF30">
-        <v>77.78</v>
+        <v>-82.93000000000001</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>217.14</v>
       </c>
       <c r="AH30" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="AI30" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="AJ30" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="AK30">
-        <v>20.00677757430309</v>
+        <v>47.9890608932856</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4036,49 +4243,49 @@
         <v>66</v>
       </c>
       <c r="B31">
-        <v>90.63846455150802</v>
+        <v>91.17647058823529</v>
       </c>
       <c r="C31">
-        <v>3382</v>
+        <v>3569</v>
       </c>
       <c r="D31">
-        <v>1117.76</v>
+        <v>53.3</v>
       </c>
       <c r="E31">
-        <v>3.93</v>
+        <v>1.07</v>
       </c>
       <c r="F31">
-        <v>-0.4434521962447718</v>
+        <v>-1.644404609190299</v>
       </c>
       <c r="G31">
-        <v>3.32</v>
+        <v>1.59</v>
       </c>
       <c r="H31">
-        <v>-0.6337090315617981</v>
+        <v>-1.363886367027739</v>
       </c>
       <c r="I31">
-        <v>1097.765966796875</v>
+        <v>53.11878662109375</v>
       </c>
       <c r="J31">
-        <v>1091.208480834961</v>
+        <v>54.20275382995605</v>
       </c>
       <c r="K31">
-        <v>1028.0337890625</v>
+        <v>51.26282875061035</v>
       </c>
       <c r="L31">
-        <v>869.3532972717285</v>
+        <v>45.59560981750488</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="N31">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="P31">
         <v>1</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -4087,58 +4294,58 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>0.5555555555555555</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="U31" t="b">
         <v>0</v>
       </c>
       <c r="V31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>290.02</v>
+        <v>28.94</v>
       </c>
       <c r="Y31">
-        <v>1236.57</v>
+        <v>56.85</v>
       </c>
       <c r="Z31">
-        <v>12.21</v>
+        <v>5.09</v>
       </c>
       <c r="AA31">
-        <v>4.9</v>
+        <v>23.07</v>
       </c>
       <c r="AB31">
-        <v>46.19</v>
+        <v>1.4</v>
       </c>
       <c r="AC31">
-        <v>79.33</v>
+        <v>311.6</v>
       </c>
       <c r="AD31">
-        <v>3.43</v>
+        <v>3.48</v>
       </c>
       <c r="AE31">
-        <v>-59.3</v>
+        <v>7.84</v>
       </c>
       <c r="AF31">
-        <v>34.08</v>
+        <v>27.75</v>
       </c>
       <c r="AG31">
-        <v>228.67</v>
+        <v>198.77</v>
       </c>
       <c r="AH31" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AI31" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="AJ31" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="AK31">
-        <v>18.55432875498792</v>
+        <v>47.43700183298665</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4146,43 +4353,43 @@
         <v>67</v>
       </c>
       <c r="B32">
-        <v>92.7927927927928</v>
+        <v>95.72032405776682</v>
       </c>
       <c r="C32">
-        <v>63</v>
+        <v>2367</v>
       </c>
       <c r="D32">
-        <v>21.8</v>
+        <v>102.43</v>
       </c>
       <c r="E32">
-        <v>6.25</v>
+        <v>2.71</v>
       </c>
       <c r="F32">
-        <v>1.069502355649157</v>
+        <v>0.05854062349913327</v>
       </c>
       <c r="G32">
-        <v>5.35</v>
+        <v>3.07</v>
       </c>
       <c r="H32">
-        <v>1.294182341023346</v>
+        <v>0.5846317611322037</v>
       </c>
       <c r="I32">
-        <v>20.07539710998535</v>
+        <v>102.5309204101563</v>
       </c>
       <c r="J32">
-        <v>18.09753475189209</v>
+        <v>107.6643623352051</v>
       </c>
       <c r="K32">
-        <v>18.33369825363159</v>
+        <v>94.57364807128906</v>
       </c>
       <c r="L32">
-        <v>11.63755249738693</v>
+        <v>73.8632017326355</v>
       </c>
       <c r="M32">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="N32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -4203,52 +4410,52 @@
         <v>0</v>
       </c>
       <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="b">
         <v>1</v>
       </c>
-      <c r="W32" t="b">
-        <v>0</v>
-      </c>
       <c r="X32">
-        <v>4.41</v>
+        <v>40.51</v>
       </c>
       <c r="Y32">
-        <v>24.11</v>
+        <v>115.19</v>
       </c>
       <c r="Z32">
-        <v>3.22</v>
+        <v>2.16</v>
       </c>
       <c r="AA32">
-        <v>0.64</v>
+        <v>162.78</v>
       </c>
       <c r="AB32">
-        <v>0.84</v>
+        <v>161.24</v>
       </c>
       <c r="AC32">
-        <v>134.78</v>
+        <v>158.33</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>6.63</v>
       </c>
       <c r="AE32">
-        <v>175.47</v>
+        <v>4.2</v>
       </c>
       <c r="AF32">
-        <v>68.45</v>
+        <v>158.7</v>
       </c>
       <c r="AG32">
-        <v>-46.09</v>
+        <v>-4.17</v>
       </c>
       <c r="AH32" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AI32" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="AJ32" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="AK32">
-        <v>17.72990414783919</v>
+        <v>47.19515716958367</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4256,43 +4463,43 @@
         <v>68</v>
       </c>
       <c r="B33">
-        <v>90.89306698002351</v>
+        <v>95.38569918985559</v>
       </c>
       <c r="C33">
-        <v>801</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>16.8</v>
+        <v>32.07</v>
       </c>
       <c r="E33">
-        <v>4.09</v>
+        <v>4.28</v>
       </c>
       <c r="F33">
-        <v>-0.339110503010708</v>
+        <v>1.688799169427431</v>
       </c>
       <c r="G33">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="H33">
-        <v>-0.1778529434628478</v>
+        <v>0.5583004350759883</v>
       </c>
       <c r="I33">
-        <v>16.33502597808838</v>
+        <v>32.16731185913086</v>
       </c>
       <c r="J33">
-        <v>16.55676884651184</v>
+        <v>31.08957023620605</v>
       </c>
       <c r="K33">
-        <v>15.17856103897095</v>
+        <v>25.83789474487305</v>
       </c>
       <c r="L33">
-        <v>10.03504544973373</v>
+        <v>19.39108383655548</v>
       </c>
       <c r="M33">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="N33">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4304,61 +4511,61 @@
         <v>0</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U33" t="b">
         <v>0</v>
       </c>
       <c r="V33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="b">
         <v>1</v>
       </c>
       <c r="X33">
-        <v>3.42</v>
+        <v>11.54</v>
       </c>
       <c r="Y33">
-        <v>18.89</v>
+        <v>34.59</v>
       </c>
       <c r="Z33">
-        <v>1.87</v>
+        <v>647.73</v>
       </c>
       <c r="AA33">
-        <v>-10.2</v>
+        <v>875.84</v>
       </c>
       <c r="AB33">
-        <v>1329.09</v>
+        <v>53.67</v>
       </c>
       <c r="AC33">
-        <v>39.13</v>
+        <v>65.83</v>
       </c>
       <c r="AD33">
-        <v>3.05</v>
+        <v>10.35</v>
       </c>
       <c r="AE33">
-        <v>-94.87</v>
+        <v>4.21</v>
       </c>
       <c r="AF33">
-        <v>20900</v>
+        <v>23.38</v>
       </c>
       <c r="AG33">
-        <v>-113.04</v>
+        <v>28.98</v>
       </c>
       <c r="AH33" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AI33" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="AJ33" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="AK33">
-        <v>13.47557316764578</v>
+        <v>46.82247269353672</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -4366,43 +4573,43 @@
         <v>69</v>
       </c>
       <c r="B34">
-        <v>92.94947121034077</v>
+        <v>96.86509334272631</v>
       </c>
       <c r="C34">
-        <v>3109</v>
+        <v>1887</v>
       </c>
       <c r="D34">
-        <v>226.13</v>
+        <v>108.86</v>
       </c>
       <c r="E34">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="F34">
-        <v>-1.043416932340641</v>
+        <v>0.8269427406882675</v>
       </c>
       <c r="G34">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="H34">
-        <v>-0.9566070939652211</v>
+        <v>0.5714660981040963</v>
       </c>
       <c r="I34">
-        <v>215.9112091064453</v>
+        <v>106.6020889282227</v>
       </c>
       <c r="J34">
-        <v>227.1712669372559</v>
+        <v>105.7293140411377</v>
       </c>
       <c r="K34">
-        <v>209.832380065918</v>
+        <v>96.80209533691406</v>
       </c>
       <c r="L34">
-        <v>157.6779619979858</v>
+        <v>81.53037464141846</v>
       </c>
       <c r="M34">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="N34">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -4423,52 +4630,4015 @@
         <v>0</v>
       </c>
       <c r="V34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="b">
         <v>1</v>
       </c>
       <c r="X34">
-        <v>41.53</v>
+        <v>39.21</v>
       </c>
       <c r="Y34">
-        <v>245.94</v>
+        <v>117.18</v>
       </c>
       <c r="Z34">
-        <v>2.05</v>
+        <v>4.07</v>
       </c>
       <c r="AA34">
-        <v>42</v>
+        <v>166.35</v>
       </c>
       <c r="AB34">
-        <v>6.72</v>
+        <v>151.12</v>
       </c>
       <c r="AC34">
-        <v>51.59</v>
+        <v>141.01</v>
       </c>
       <c r="AD34">
-        <v>17.8</v>
+        <v>23.42</v>
       </c>
       <c r="AE34">
-        <v>-18.77</v>
+        <v>16.26</v>
       </c>
       <c r="AF34">
-        <v>57.53</v>
+        <v>40.84</v>
       </c>
       <c r="AG34">
-        <v>18.47</v>
+        <v>47.19</v>
       </c>
       <c r="AH34" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK34">
+        <v>46.09323068255343</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37">
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35">
+        <v>94.17048256428319</v>
+      </c>
+      <c r="C35">
+        <v>1895</v>
+      </c>
+      <c r="D35">
+        <v>68.5</v>
+      </c>
+      <c r="E35">
+        <v>2.13</v>
+      </c>
+      <c r="F35">
+        <v>-0.5437204953788366</v>
+      </c>
+      <c r="G35">
+        <v>3.18</v>
+      </c>
+      <c r="H35">
+        <v>0.7294540544413891</v>
+      </c>
+      <c r="I35">
+        <v>68.01600189208985</v>
+      </c>
+      <c r="J35">
+        <v>68.75600090026856</v>
+      </c>
+      <c r="K35">
+        <v>59.04000030517578</v>
+      </c>
+      <c r="L35">
+        <v>45.699800157547</v>
+      </c>
+      <c r="M35">
+        <v>0.99</v>
+      </c>
+      <c r="N35">
+        <v>1.15</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35" t="b">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>30.18</v>
+      </c>
+      <c r="Y35">
+        <v>72.8</v>
+      </c>
+      <c r="Z35">
+        <v>3.93</v>
+      </c>
+      <c r="AA35">
+        <v>-4.54</v>
+      </c>
+      <c r="AB35">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="AC35">
+        <v>135.29</v>
+      </c>
+      <c r="AD35">
+        <v>2.02</v>
+      </c>
+      <c r="AE35">
+        <v>1100</v>
+      </c>
+      <c r="AF35">
+        <v>-80</v>
+      </c>
+      <c r="AG35">
+        <v>114.71</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK35">
+        <v>44.62908620185672</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36">
+        <v>90.01408946812258</v>
+      </c>
+      <c r="C36">
+        <v>1544</v>
+      </c>
+      <c r="D36">
+        <v>285.32</v>
+      </c>
+      <c r="E36">
+        <v>2.03</v>
+      </c>
+      <c r="F36">
+        <v>-0.6475586193233143</v>
+      </c>
+      <c r="G36">
+        <v>1.84</v>
+      </c>
+      <c r="H36">
+        <v>-1.034744791325046</v>
+      </c>
+      <c r="I36">
+        <v>276.3002868652344</v>
+      </c>
+      <c r="J36">
+        <v>278.0228149414062</v>
+      </c>
+      <c r="K36">
+        <v>266.4480709838867</v>
+      </c>
+      <c r="L36">
+        <v>233.5415275573731</v>
+      </c>
+      <c r="M36">
+        <v>0.99</v>
+      </c>
+      <c r="N36">
+        <v>1.04</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>1</v>
+      </c>
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>158.01</v>
+      </c>
+      <c r="Y36">
+        <v>286.01</v>
+      </c>
+      <c r="Z36">
+        <v>30.69</v>
+      </c>
+      <c r="AA36">
+        <v>4.52</v>
+      </c>
+      <c r="AB36">
+        <v>27.68</v>
+      </c>
+      <c r="AC36">
+        <v>175.41</v>
+      </c>
+      <c r="AD36">
+        <v>5.81</v>
+      </c>
+      <c r="AE36">
+        <v>-5.08</v>
+      </c>
+      <c r="AF36">
+        <v>6.63</v>
+      </c>
+      <c r="AG36">
+        <v>172.13</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>169</v>
+      </c>
+      <c r="AK36">
+        <v>44.34895005655675</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37">
+        <v>94.94540331102502</v>
+      </c>
+      <c r="C37">
+        <v>1835</v>
+      </c>
+      <c r="D37">
+        <v>63.99</v>
+      </c>
+      <c r="E37">
+        <v>2.07</v>
+      </c>
+      <c r="F37">
+        <v>-0.6060233697455233</v>
+      </c>
+      <c r="G37">
+        <v>2.23</v>
+      </c>
+      <c r="H37">
+        <v>-0.5212839332288447</v>
+      </c>
+      <c r="I37">
+        <v>62.86600036621094</v>
+      </c>
+      <c r="J37">
+        <v>62.34450073242188</v>
+      </c>
+      <c r="K37">
+        <v>54.79960037231445</v>
+      </c>
+      <c r="L37">
+        <v>44.79590007781982</v>
+      </c>
+      <c r="M37">
+        <v>1.01</v>
+      </c>
+      <c r="N37">
+        <v>1.15</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>3</v>
+      </c>
+      <c r="T37">
+        <v>6.111111111111111</v>
+      </c>
+      <c r="U37" t="b">
+        <v>1</v>
+      </c>
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>27.76</v>
+      </c>
+      <c r="Y37">
+        <v>67.19</v>
+      </c>
+      <c r="Z37">
+        <v>1.6</v>
+      </c>
+      <c r="AA37">
+        <v>303.75</v>
+      </c>
+      <c r="AB37">
+        <v>29.05</v>
+      </c>
+      <c r="AC37">
+        <v>86.36</v>
+      </c>
+      <c r="AD37">
+        <v>5.38</v>
+      </c>
+      <c r="AE37">
+        <v>46.43</v>
+      </c>
+      <c r="AF37">
+        <v>14.29</v>
+      </c>
+      <c r="AG37">
+        <v>11.36</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK37">
+        <v>44.20005523413929</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37">
+      <c r="A38" t="s">
         <v>73</v>
       </c>
-      <c r="AI34" t="s">
+      <c r="B38">
+        <v>90.63050369848538</v>
+      </c>
+      <c r="C38">
+        <v>1616</v>
+      </c>
+      <c r="D38">
+        <v>34.28</v>
+      </c>
+      <c r="E38">
+        <v>4.4</v>
+      </c>
+      <c r="F38">
+        <v>1.813404918160805</v>
+      </c>
+      <c r="G38">
+        <v>4.36</v>
+      </c>
+      <c r="H38">
+        <v>2.283002291758101</v>
+      </c>
+      <c r="I38">
+        <v>34.93399887084961</v>
+      </c>
+      <c r="J38">
+        <v>37.07049942016602</v>
+      </c>
+      <c r="K38">
+        <v>32.31639984130859</v>
+      </c>
+      <c r="L38">
+        <v>24.87304999351501</v>
+      </c>
+      <c r="M38">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N38">
+        <v>1.08</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>16.55</v>
+      </c>
+      <c r="Y38">
+        <v>42.01</v>
+      </c>
+      <c r="Z38">
+        <v>1.58</v>
+      </c>
+      <c r="AA38">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="AB38">
+        <v>41.46</v>
+      </c>
+      <c r="AC38">
+        <v>150</v>
+      </c>
+      <c r="AD38">
+        <v>1.33</v>
+      </c>
+      <c r="AE38">
+        <v>142.86</v>
+      </c>
+      <c r="AF38">
+        <v>50</v>
+      </c>
+      <c r="AG38">
+        <v>-133.33</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK38">
+        <v>43.8832095563797</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39">
+        <v>95.47375836562169</v>
+      </c>
+      <c r="C39">
+        <v>2444.5</v>
+      </c>
+      <c r="D39">
+        <v>43.83</v>
+      </c>
+      <c r="E39">
+        <v>3.46</v>
+      </c>
+      <c r="F39">
+        <v>0.837326553082715</v>
+      </c>
+      <c r="G39">
+        <v>2.84</v>
+      </c>
+      <c r="H39">
+        <v>0.2818215114857262</v>
+      </c>
+      <c r="I39">
+        <v>44.68536911010742</v>
+      </c>
+      <c r="J39">
+        <v>44.56681957244873</v>
+      </c>
+      <c r="K39">
+        <v>41.46530883789062</v>
+      </c>
+      <c r="L39">
+        <v>35.83000336647034</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>1.08</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>1</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>18.21</v>
+      </c>
+      <c r="Y39">
+        <v>48.8</v>
+      </c>
+      <c r="Z39">
+        <v>1.78</v>
+      </c>
+      <c r="AA39">
+        <v>-528.9299999999999</v>
+      </c>
+      <c r="AB39">
+        <v>93.94</v>
+      </c>
+      <c r="AC39">
+        <v>121.05</v>
+      </c>
+      <c r="AD39">
+        <v>6.63</v>
+      </c>
+      <c r="AE39">
+        <v>16.67</v>
+      </c>
+      <c r="AF39">
+        <v>16.13</v>
+      </c>
+      <c r="AG39">
+        <v>63.16</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK39">
+        <v>43.81740432851583</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37">
+      <c r="A40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40">
+        <v>90.27826699542092</v>
+      </c>
+      <c r="C40">
+        <v>454</v>
+      </c>
+      <c r="D40">
+        <v>32.36</v>
+      </c>
+      <c r="E40">
+        <v>3.75</v>
+      </c>
+      <c r="F40">
+        <v>1.1384571125217</v>
+      </c>
+      <c r="G40">
+        <v>2.53</v>
+      </c>
+      <c r="H40">
+        <v>-0.1263140423856133</v>
+      </c>
+      <c r="I40">
+        <v>32.4060001373291</v>
+      </c>
+      <c r="J40">
+        <v>29.08412485122681</v>
+      </c>
+      <c r="K40">
+        <v>26.91759998321533</v>
+      </c>
+      <c r="L40">
+        <v>24.56593753814697</v>
+      </c>
+      <c r="M40">
+        <v>1.11</v>
+      </c>
+      <c r="N40">
+        <v>1.2</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="W40" t="b">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>17.44</v>
+      </c>
+      <c r="Y40">
+        <v>33.31</v>
+      </c>
+      <c r="Z40">
+        <v>1.49</v>
+      </c>
+      <c r="AA40">
+        <v>77.63</v>
+      </c>
+      <c r="AB40">
+        <v>31.16</v>
+      </c>
+      <c r="AC40">
+        <v>132.43</v>
+      </c>
+      <c r="AD40">
+        <v>2.08</v>
+      </c>
+      <c r="AE40">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="AF40">
+        <v>120.93</v>
+      </c>
+      <c r="AG40">
+        <v>16.22</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK40">
+        <v>42.25335262806752</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41">
+        <v>97.8513561113068</v>
+      </c>
+      <c r="C41">
+        <v>1707</v>
+      </c>
+      <c r="D41">
+        <v>59.82</v>
+      </c>
+      <c r="E41">
+        <v>2.46</v>
+      </c>
+      <c r="F41">
+        <v>-0.2010546863620606</v>
+      </c>
+      <c r="G41">
+        <v>2.73</v>
+      </c>
+      <c r="H41">
+        <v>0.1369992181765414</v>
+      </c>
+      <c r="I41">
+        <v>57.95</v>
+      </c>
+      <c r="J41">
+        <v>58.28250064849853</v>
+      </c>
+      <c r="K41">
+        <v>51.11860054016113</v>
+      </c>
+      <c r="L41">
+        <v>39.6372002029419</v>
+      </c>
+      <c r="M41">
+        <v>0.99</v>
+      </c>
+      <c r="N41">
+        <v>1.13</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="W41" t="b">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>17.32</v>
+      </c>
+      <c r="Y41">
+        <v>61.48</v>
+      </c>
+      <c r="Z41">
+        <v>1.46</v>
+      </c>
+      <c r="AA41">
+        <v>16.07</v>
+      </c>
+      <c r="AB41">
+        <v>74.83</v>
+      </c>
+      <c r="AC41">
+        <v>102.38</v>
+      </c>
+      <c r="AD41">
+        <v>10.12</v>
+      </c>
+      <c r="AE41">
+        <v>88.89</v>
+      </c>
+      <c r="AF41">
+        <v>73.08</v>
+      </c>
+      <c r="AG41">
+        <v>-38.1</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK41">
+        <v>41.94625770868808</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37">
+      <c r="A42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42">
+        <v>95.19196900317013</v>
+      </c>
+      <c r="C42">
+        <v>818</v>
+      </c>
+      <c r="D42">
+        <v>200.35</v>
+      </c>
+      <c r="E42">
+        <v>4.78</v>
+      </c>
+      <c r="F42">
+        <v>2.207989789149819</v>
+      </c>
+      <c r="G42">
+        <v>3.79</v>
+      </c>
+      <c r="H42">
+        <v>1.53255949915596</v>
+      </c>
+      <c r="I42">
+        <v>187.7640045166016</v>
+      </c>
+      <c r="J42">
+        <v>190.1980010986328</v>
+      </c>
+      <c r="K42">
+        <v>176.4180014038086</v>
+      </c>
+      <c r="L42">
+        <v>123.2045503234863</v>
+      </c>
+      <c r="M42">
+        <v>0.99</v>
+      </c>
+      <c r="N42">
+        <v>1.06</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="W42" t="b">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>82.59</v>
+      </c>
+      <c r="Y42">
+        <v>227.59</v>
+      </c>
+      <c r="Z42">
+        <v>7.26</v>
+      </c>
+      <c r="AA42">
+        <v>-4.5</v>
+      </c>
+      <c r="AB42">
+        <v>60.48</v>
+      </c>
+      <c r="AC42">
+        <v>105.71</v>
+      </c>
+      <c r="AD42">
+        <v>0.14</v>
+      </c>
+      <c r="AE42">
+        <v>110</v>
+      </c>
+      <c r="AF42">
+        <v>33.33</v>
+      </c>
+      <c r="AG42">
+        <v>14.29</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK42">
+        <v>41.76407015212709</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37">
+      <c r="A43" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43">
+        <v>90.78901021486439</v>
+      </c>
+      <c r="C43">
+        <v>439</v>
+      </c>
+      <c r="D43">
+        <v>126.44</v>
+      </c>
+      <c r="E43">
+        <v>2.14</v>
+      </c>
+      <c r="F43">
+        <v>-0.5333366829843886</v>
+      </c>
+      <c r="G43">
+        <v>1.98</v>
+      </c>
+      <c r="H43">
+        <v>-0.8504255089315378</v>
+      </c>
+      <c r="I43">
+        <v>128.6934616088867</v>
+      </c>
+      <c r="J43">
+        <v>136.5032558441162</v>
+      </c>
+      <c r="K43">
+        <v>124.6575079345703</v>
+      </c>
+      <c r="L43">
+        <v>107.4324875640869</v>
+      </c>
+      <c r="M43">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N43">
+        <v>1.03</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="b">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="Y43">
+        <v>142.47</v>
+      </c>
+      <c r="Z43">
+        <v>35.56</v>
+      </c>
+      <c r="AA43">
+        <v>2.42</v>
+      </c>
+      <c r="AB43">
+        <v>17.33</v>
+      </c>
+      <c r="AC43">
+        <v>143.53</v>
+      </c>
+      <c r="AD43">
+        <v>20.32</v>
+      </c>
+      <c r="AE43">
+        <v>10.11</v>
+      </c>
+      <c r="AF43">
+        <v>38.24</v>
+      </c>
+      <c r="AG43">
+        <v>60</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK43">
+        <v>41.72279524837393</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37">
+      <c r="A44" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44">
+        <v>90.75378654455794</v>
+      </c>
+      <c r="C44">
+        <v>2220</v>
+      </c>
+      <c r="D44">
+        <v>271</v>
+      </c>
+      <c r="E44">
+        <v>0.26</v>
+      </c>
+      <c r="F44">
+        <v>-2.485493413140567</v>
+      </c>
+      <c r="G44">
+        <v>4.01</v>
+      </c>
+      <c r="H44">
+        <v>1.82220408577433</v>
+      </c>
+      <c r="I44">
+        <v>271.2900024414063</v>
+      </c>
+      <c r="J44">
+        <v>270.2559982299805</v>
+      </c>
+      <c r="K44">
+        <v>225.3561987304687</v>
+      </c>
+      <c r="L44">
+        <v>200.9907493591309</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>1.2</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44" t="b">
+        <v>1</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>146.02</v>
+      </c>
+      <c r="Y44">
+        <v>273</v>
+      </c>
+      <c r="Z44">
+        <v>3.52</v>
+      </c>
+      <c r="AA44">
+        <v>11.52</v>
+      </c>
+      <c r="AB44">
+        <v>374.34</v>
+      </c>
+      <c r="AC44">
+        <v>63.41</v>
+      </c>
+      <c r="AD44">
+        <v>2.29</v>
+      </c>
+      <c r="AE44">
+        <v>-12.42</v>
+      </c>
+      <c r="AF44">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="AG44">
+        <v>103.66</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK44">
+        <v>41.3956343303133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37">
+      <c r="A45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45">
+        <v>93.4836209933075</v>
+      </c>
+      <c r="C45">
+        <v>1075</v>
+      </c>
+      <c r="D45">
+        <v>67.78</v>
+      </c>
+      <c r="E45">
+        <v>2.4</v>
+      </c>
+      <c r="F45">
+        <v>-0.2633575607287472</v>
+      </c>
+      <c r="G45">
+        <v>2.49</v>
+      </c>
+      <c r="H45">
+        <v>-0.1789766944980436</v>
+      </c>
+      <c r="I45">
+        <v>65.24303283691407</v>
+      </c>
+      <c r="J45">
+        <v>65.0189868927002</v>
+      </c>
+      <c r="K45">
+        <v>62.4691130065918</v>
+      </c>
+      <c r="L45">
+        <v>58.14686164855957</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>1.04</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="W45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>32.56</v>
+      </c>
+      <c r="Y45">
+        <v>72.81</v>
+      </c>
+      <c r="Z45">
+        <v>5.53</v>
+      </c>
+      <c r="AA45">
+        <v>289.15</v>
+      </c>
+      <c r="AB45">
+        <v>247.3</v>
+      </c>
+      <c r="AC45">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AD45">
+        <v>24.25</v>
+      </c>
+      <c r="AE45">
+        <v>-20.89</v>
+      </c>
+      <c r="AF45">
+        <v>63.25</v>
+      </c>
+      <c r="AG45">
+        <v>30.17</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>157</v>
+      </c>
+      <c r="AK45">
+        <v>41.10250793237715</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37">
+      <c r="A46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46">
+        <v>98.09792180345191</v>
+      </c>
+      <c r="C46">
+        <v>2552</v>
+      </c>
+      <c r="D46">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E46">
+        <v>3.43</v>
+      </c>
+      <c r="F46">
+        <v>0.8061751158993719</v>
+      </c>
+      <c r="G46">
+        <v>2.63</v>
+      </c>
+      <c r="H46">
+        <v>0.00534258789546405</v>
+      </c>
+      <c r="I46">
+        <v>83.42889709472657</v>
+      </c>
+      <c r="J46">
+        <v>87.51743431091309</v>
+      </c>
+      <c r="K46">
+        <v>80.14443237304687</v>
+      </c>
+      <c r="L46">
+        <v>61.32414295196534</v>
+      </c>
+      <c r="M46">
+        <v>0.95</v>
+      </c>
+      <c r="N46">
+        <v>1.04</v>
+      </c>
+      <c r="P46">
+        <v>2</v>
+      </c>
+      <c r="Q46">
+        <v>2</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="b">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>22.8</v>
+      </c>
+      <c r="Y46">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="Z46">
+        <v>1.44</v>
+      </c>
+      <c r="AA46">
+        <v>2050.84</v>
+      </c>
+      <c r="AB46">
+        <v>10.52</v>
+      </c>
+      <c r="AC46">
+        <v>102.13</v>
+      </c>
+      <c r="AD46">
+        <v>3.82</v>
+      </c>
+      <c r="AE46">
+        <v>-1.63</v>
+      </c>
+      <c r="AF46">
+        <v>269.27</v>
+      </c>
+      <c r="AG46">
+        <v>98.72</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK46">
+        <v>40.97976068087677</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37">
+      <c r="A47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47">
+        <v>90.85945755547729</v>
+      </c>
+      <c r="C47">
+        <v>1437</v>
+      </c>
+      <c r="D47">
+        <v>135.26</v>
+      </c>
+      <c r="E47">
+        <v>3.63</v>
+      </c>
+      <c r="F47">
+        <v>1.013851363788327</v>
+      </c>
+      <c r="G47">
+        <v>2.93</v>
+      </c>
+      <c r="H47">
+        <v>0.4003124787386961</v>
+      </c>
+      <c r="I47">
+        <v>133.2239990234375</v>
+      </c>
+      <c r="J47">
+        <v>129.1780010223389</v>
+      </c>
+      <c r="K47">
+        <v>112.6288003540039</v>
+      </c>
+      <c r="L47">
+        <v>103.6115000534058</v>
+      </c>
+      <c r="M47">
+        <v>1.03</v>
+      </c>
+      <c r="N47">
+        <v>1.18</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>3</v>
+      </c>
+      <c r="S47">
+        <v>2</v>
+      </c>
+      <c r="T47">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="U47" t="b">
+        <v>1</v>
+      </c>
+      <c r="V47" t="b">
+        <v>1</v>
+      </c>
+      <c r="W47" t="b">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="Y47">
+        <v>138.9</v>
+      </c>
+      <c r="Z47">
+        <v>11.79</v>
+      </c>
+      <c r="AA47">
+        <v>93.5</v>
+      </c>
+      <c r="AB47">
+        <v>7.4</v>
+      </c>
+      <c r="AC47">
+        <v>72.97</v>
+      </c>
+      <c r="AD47">
+        <v>10.24</v>
+      </c>
+      <c r="AE47">
+        <v>20.75</v>
+      </c>
+      <c r="AF47">
+        <v>26.19</v>
+      </c>
+      <c r="AG47">
+        <v>13.51</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>157</v>
+      </c>
+      <c r="AK47">
+        <v>40.59727726662812</v>
+      </c>
+    </row>
+    <row r="48" spans="1:37">
+      <c r="A48" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48">
+        <v>92.84959492779149</v>
+      </c>
+      <c r="C48">
+        <v>342</v>
+      </c>
+      <c r="D48">
+        <v>20.88</v>
+      </c>
+      <c r="E48">
+        <v>3.87</v>
+      </c>
+      <c r="F48">
+        <v>1.263062861255073</v>
+      </c>
+      <c r="G48">
+        <v>3.33</v>
+      </c>
+      <c r="H48">
+        <v>0.9269389998630048</v>
+      </c>
+      <c r="I48">
+        <v>20.62400016784668</v>
+      </c>
+      <c r="J48">
+        <v>22.24250001907349</v>
+      </c>
+      <c r="K48">
+        <v>20.34920001983643</v>
+      </c>
+      <c r="L48">
+        <v>18.06164999961853</v>
+      </c>
+      <c r="M48">
+        <v>0.93</v>
+      </c>
+      <c r="N48">
+        <v>1.01</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+      <c r="V48" t="b">
+        <v>0</v>
+      </c>
+      <c r="W48" t="b">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="Y48">
+        <v>24.89</v>
+      </c>
+      <c r="Z48">
+        <v>5.06</v>
+      </c>
+      <c r="AA48">
+        <v>1.85</v>
+      </c>
+      <c r="AB48">
+        <v>115.22</v>
+      </c>
+      <c r="AC48">
+        <v>67.86</v>
+      </c>
+      <c r="AD48">
+        <v>2.97</v>
+      </c>
+      <c r="AE48">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="AF48">
+        <v>440</v>
+      </c>
+      <c r="AG48">
+        <v>-82.14</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>172</v>
+      </c>
+      <c r="AK48">
+        <v>39.4525930394101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:37">
+      <c r="A49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49">
+        <v>97.27016555125044</v>
+      </c>
+      <c r="C49">
+        <v>1890</v>
+      </c>
+      <c r="D49">
+        <v>122.2</v>
+      </c>
+      <c r="E49">
+        <v>2.41</v>
+      </c>
+      <c r="F49">
+        <v>-0.2529737483342992</v>
+      </c>
+      <c r="G49">
+        <v>2.39</v>
+      </c>
+      <c r="H49">
+        <v>-0.310633324779121</v>
+      </c>
+      <c r="I49">
+        <v>122.9299987792969</v>
+      </c>
+      <c r="J49">
+        <v>123.2299995422363</v>
+      </c>
+      <c r="K49">
+        <v>108.0217994689941</v>
+      </c>
+      <c r="L49">
+        <v>83.66379983901977</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>1.14</v>
+      </c>
+      <c r="P49">
+        <v>2</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>7</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>8.888888888888888</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49" t="b">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>39.28</v>
+      </c>
+      <c r="Y49">
+        <v>134.5</v>
+      </c>
+      <c r="Z49">
+        <v>2.7</v>
+      </c>
+      <c r="AA49">
+        <v>122.5</v>
+      </c>
+      <c r="AB49">
+        <v>99.56</v>
+      </c>
+      <c r="AC49">
+        <v>25.49</v>
+      </c>
+      <c r="AD49">
+        <v>7.87</v>
+      </c>
+      <c r="AE49">
+        <v>-7.25</v>
+      </c>
+      <c r="AF49">
+        <v>62.35</v>
+      </c>
+      <c r="AG49">
+        <v>-16.67</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK49">
+        <v>39.34283455158435</v>
+      </c>
+    </row>
+    <row r="50" spans="1:37">
+      <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50">
+        <v>92.49735822472702</v>
+      </c>
+      <c r="C50">
+        <v>3355</v>
+      </c>
+      <c r="D50">
+        <v>643.11</v>
+      </c>
+      <c r="E50">
+        <v>1.56</v>
+      </c>
+      <c r="F50">
+        <v>-1.135597801862358</v>
+      </c>
+      <c r="G50">
+        <v>2.34</v>
+      </c>
+      <c r="H50">
+        <v>-0.3764616399196599</v>
+      </c>
+      <c r="I50">
+        <v>635.5980102539063</v>
+      </c>
+      <c r="J50">
+        <v>656.67900390625</v>
+      </c>
+      <c r="K50">
+        <v>629.5092041015625</v>
+      </c>
+      <c r="L50">
+        <v>497.7412506103516</v>
+      </c>
+      <c r="M50">
+        <v>0.97</v>
+      </c>
+      <c r="N50">
+        <v>1.01</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50" t="b">
+        <v>1</v>
+      </c>
+      <c r="V50" t="b">
+        <v>1</v>
+      </c>
+      <c r="W50" t="b">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>320.19</v>
+      </c>
+      <c r="Y50">
+        <v>703.27</v>
+      </c>
+      <c r="Z50">
+        <v>9.26</v>
+      </c>
+      <c r="AA50">
+        <v>2.64</v>
+      </c>
+      <c r="AB50">
+        <v>67.95</v>
+      </c>
+      <c r="AC50">
+        <v>71.88</v>
+      </c>
+      <c r="AD50">
+        <v>12.8</v>
+      </c>
+      <c r="AE50">
+        <v>-7.91</v>
+      </c>
+      <c r="AF50">
+        <v>45.06</v>
+      </c>
+      <c r="AG50">
+        <v>28.66</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK50">
+        <v>38.8134213450693</v>
+      </c>
+    </row>
+    <row r="51" spans="1:37">
+      <c r="A51" t="s">
         <v>86</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK34">
-        <v>6.868608988880974</v>
+      <c r="B51">
+        <v>90.19020781965482</v>
+      </c>
+      <c r="C51">
+        <v>1114</v>
+      </c>
+      <c r="D51">
+        <v>75.45</v>
+      </c>
+      <c r="E51">
+        <v>2.86</v>
+      </c>
+      <c r="F51">
+        <v>0.2142978094158495</v>
+      </c>
+      <c r="G51">
+        <v>2.41</v>
+      </c>
+      <c r="H51">
+        <v>-0.2843019987229055</v>
+      </c>
+      <c r="I51">
+        <v>75.99199829101562</v>
+      </c>
+      <c r="J51">
+        <v>80.65799980163574</v>
+      </c>
+      <c r="K51">
+        <v>72.58199996948242</v>
+      </c>
+      <c r="L51">
+        <v>57.75044994354248</v>
+      </c>
+      <c r="M51">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N51">
+        <v>1.05</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+      <c r="V51" t="b">
+        <v>0</v>
+      </c>
+      <c r="W51" t="b">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>37.38</v>
+      </c>
+      <c r="Y51">
+        <v>85.45</v>
+      </c>
+      <c r="Z51">
+        <v>9.16</v>
+      </c>
+      <c r="AA51">
+        <v>-17.57</v>
+      </c>
+      <c r="AB51">
+        <v>34.78</v>
+      </c>
+      <c r="AC51">
+        <v>66.67</v>
+      </c>
+      <c r="AD51">
+        <v>6.81</v>
+      </c>
+      <c r="AE51">
+        <v>25</v>
+      </c>
+      <c r="AF51">
+        <v>14.29</v>
+      </c>
+      <c r="AG51">
+        <v>16.67</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK51">
+        <v>36.7913192385134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:37">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52">
+        <v>91.5639309616062</v>
+      </c>
+      <c r="C52">
+        <v>2581</v>
+      </c>
+      <c r="D52">
+        <v>37.25</v>
+      </c>
+      <c r="E52">
+        <v>2.26</v>
+      </c>
+      <c r="F52">
+        <v>-0.4087309342510159</v>
+      </c>
+      <c r="G52">
+        <v>2.2</v>
+      </c>
+      <c r="H52">
+        <v>-0.5607809223131676</v>
+      </c>
+      <c r="I52">
+        <v>36.31256484985352</v>
+      </c>
+      <c r="J52">
+        <v>37.91323642730713</v>
+      </c>
+      <c r="K52">
+        <v>36.92305404663086</v>
+      </c>
+      <c r="L52">
+        <v>32.11488737106323</v>
+      </c>
+      <c r="M52">
+        <v>0.96</v>
+      </c>
+      <c r="N52">
+        <v>0.98</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52" t="b">
+        <v>0</v>
+      </c>
+      <c r="V52" t="b">
+        <v>1</v>
+      </c>
+      <c r="W52" t="b">
+        <v>1</v>
+      </c>
+      <c r="X52">
+        <v>19.59</v>
+      </c>
+      <c r="Y52">
+        <v>41.08</v>
+      </c>
+      <c r="Z52">
+        <v>1.78</v>
+      </c>
+      <c r="AA52">
+        <v>25</v>
+      </c>
+      <c r="AB52">
+        <v>20.69</v>
+      </c>
+      <c r="AC52">
+        <v>63.04</v>
+      </c>
+      <c r="AD52">
+        <v>2.87</v>
+      </c>
+      <c r="AE52">
+        <v>25</v>
+      </c>
+      <c r="AF52">
+        <v>-6.25</v>
+      </c>
+      <c r="AG52">
+        <v>39.13</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK52">
+        <v>35.26063800035959</v>
+      </c>
+    </row>
+    <row r="53" spans="1:37">
+      <c r="A53" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53">
+        <v>91.7928848185981</v>
+      </c>
+      <c r="C53">
+        <v>2315</v>
+      </c>
+      <c r="D53">
+        <v>171.04</v>
+      </c>
+      <c r="E53">
+        <v>1.74</v>
+      </c>
+      <c r="F53">
+        <v>-0.9486891787622991</v>
+      </c>
+      <c r="G53">
+        <v>2.48</v>
+      </c>
+      <c r="H53">
+        <v>-0.1921423575261517</v>
+      </c>
+      <c r="I53">
+        <v>170.6641876220703</v>
+      </c>
+      <c r="J53">
+        <v>178.1145202636719</v>
+      </c>
+      <c r="K53">
+        <v>167.4995913696289</v>
+      </c>
+      <c r="L53">
+        <v>160.7103205871582</v>
+      </c>
+      <c r="M53">
+        <v>0.96</v>
+      </c>
+      <c r="N53">
+        <v>1.02</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>2</v>
+      </c>
+      <c r="T53">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="b">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>90.14</v>
+      </c>
+      <c r="Y53">
+        <v>191.46</v>
+      </c>
+      <c r="Z53">
+        <v>6.69</v>
+      </c>
+      <c r="AA53">
+        <v>1.8</v>
+      </c>
+      <c r="AB53">
+        <v>149.79</v>
+      </c>
+      <c r="AC53">
+        <v>25.81</v>
+      </c>
+      <c r="AD53">
+        <v>6.51</v>
+      </c>
+      <c r="AE53">
+        <v>19.08</v>
+      </c>
+      <c r="AF53">
+        <v>-25.57</v>
+      </c>
+      <c r="AG53">
+        <v>41.94</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK53">
+        <v>35.18020072089502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:37">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54">
+        <v>92.65586474110602</v>
+      </c>
+      <c r="C54">
+        <v>2591</v>
+      </c>
+      <c r="D54">
+        <v>84.41</v>
+      </c>
+      <c r="E54">
+        <v>3.37</v>
+      </c>
+      <c r="F54">
+        <v>0.7438722415326853</v>
+      </c>
+      <c r="G54">
+        <v>2.84</v>
+      </c>
+      <c r="H54">
+        <v>0.2818215114857262</v>
+      </c>
+      <c r="I54">
+        <v>79.03819274902344</v>
+      </c>
+      <c r="J54">
+        <v>74.57213554382324</v>
+      </c>
+      <c r="K54">
+        <v>69.12628425598145</v>
+      </c>
+      <c r="L54">
+        <v>64.89926876068115</v>
+      </c>
+      <c r="M54">
+        <v>1.06</v>
+      </c>
+      <c r="N54">
+        <v>1.14</v>
+      </c>
+      <c r="P54">
+        <v>2</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+      <c r="V54" t="b">
+        <v>1</v>
+      </c>
+      <c r="W54" t="b">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>42.01</v>
+      </c>
+      <c r="Y54">
+        <v>85.93000000000001</v>
+      </c>
+      <c r="Z54">
+        <v>1.41</v>
+      </c>
+      <c r="AA54">
+        <v>14.79</v>
+      </c>
+      <c r="AB54">
+        <v>14.38</v>
+      </c>
+      <c r="AC54">
+        <v>56.52</v>
+      </c>
+      <c r="AD54">
+        <v>3.85</v>
+      </c>
+      <c r="AE54">
+        <v>18.68</v>
+      </c>
+      <c r="AF54">
+        <v>1.11</v>
+      </c>
+      <c r="AG54">
+        <v>30.43</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>135</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>175</v>
+      </c>
+      <c r="AK54">
+        <v>34.65246674533038</v>
+      </c>
+    </row>
+    <row r="55" spans="1:37">
+      <c r="A55" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55">
+        <v>92.28601620288835</v>
+      </c>
+      <c r="C55">
+        <v>1755</v>
+      </c>
+      <c r="D55">
+        <v>53.17</v>
+      </c>
+      <c r="E55">
+        <v>1.4</v>
+      </c>
+      <c r="F55">
+        <v>-1.301738800173523</v>
+      </c>
+      <c r="G55">
+        <v>1.58</v>
+      </c>
+      <c r="H55">
+        <v>-1.377052030055846</v>
+      </c>
+      <c r="I55">
+        <v>52.13324584960937</v>
+      </c>
+      <c r="J55">
+        <v>52.47992343902588</v>
+      </c>
+      <c r="K55">
+        <v>50.24906402587891</v>
+      </c>
+      <c r="L55">
+        <v>42.80892195701599</v>
+      </c>
+      <c r="M55">
+        <v>0.99</v>
+      </c>
+      <c r="N55">
+        <v>1.04</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <v>1</v>
+      </c>
+      <c r="V55" t="b">
+        <v>1</v>
+      </c>
+      <c r="W55" t="b">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>27.18</v>
+      </c>
+      <c r="Y55">
+        <v>55.01</v>
+      </c>
+      <c r="Z55">
+        <v>6.26</v>
+      </c>
+      <c r="AA55">
+        <v>22.45</v>
+      </c>
+      <c r="AB55">
+        <v>59.42</v>
+      </c>
+      <c r="AC55">
+        <v>40.91</v>
+      </c>
+      <c r="AD55">
+        <v>2.02</v>
+      </c>
+      <c r="AE55">
+        <v>-6.06</v>
+      </c>
+      <c r="AF55">
+        <v>37.5</v>
+      </c>
+      <c r="AG55">
+        <v>9.09</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK55">
+        <v>33.89466934872443</v>
+      </c>
+    </row>
+    <row r="56" spans="1:37">
+      <c r="A56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56">
+        <v>94.5579429376541</v>
+      </c>
+      <c r="C56">
+        <v>4229</v>
+      </c>
+      <c r="D56">
+        <v>563.17</v>
+      </c>
+      <c r="E56">
+        <v>3.34</v>
+      </c>
+      <c r="F56">
+        <v>0.7127208043493418</v>
+      </c>
+      <c r="G56">
+        <v>2.38</v>
+      </c>
+      <c r="H56">
+        <v>-0.323798987807229</v>
+      </c>
+      <c r="I56">
+        <v>559.5709716796875</v>
+      </c>
+      <c r="J56">
+        <v>508.1176864624023</v>
+      </c>
+      <c r="K56">
+        <v>434.0768695068359</v>
+      </c>
+      <c r="L56">
+        <v>366.7743074798584</v>
+      </c>
+      <c r="M56">
+        <v>1.1</v>
+      </c>
+      <c r="N56">
+        <v>1.29</v>
+      </c>
+      <c r="O56" t="s">
+        <v>106</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>10</v>
+      </c>
+      <c r="T56">
+        <v>17.77777777777778</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+      <c r="V56" t="b">
+        <v>1</v>
+      </c>
+      <c r="W56" t="b">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>243.34</v>
+      </c>
+      <c r="Y56">
+        <v>585.95</v>
+      </c>
+      <c r="Z56">
+        <v>4.45</v>
+      </c>
+      <c r="AA56">
+        <v>14.76</v>
+      </c>
+      <c r="AB56">
+        <v>45.94</v>
+      </c>
+      <c r="AC56">
+        <v>3.86</v>
+      </c>
+      <c r="AD56">
+        <v>10.13</v>
+      </c>
+      <c r="AE56">
+        <v>43.07</v>
+      </c>
+      <c r="AF56">
+        <v>-9.67</v>
+      </c>
+      <c r="AG56">
+        <v>-19.64</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>135</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK56">
+        <v>31.71043547666315</v>
+      </c>
+    </row>
+    <row r="57" spans="1:37">
+      <c r="A57" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57">
+        <v>91.52870729129975</v>
+      </c>
+      <c r="C57">
+        <v>4982</v>
+      </c>
+      <c r="D57">
+        <v>23.44</v>
+      </c>
+      <c r="E57">
+        <v>2.17</v>
+      </c>
+      <c r="F57">
+        <v>-0.5021852458010456</v>
+      </c>
+      <c r="G57">
+        <v>2.48</v>
+      </c>
+      <c r="H57">
+        <v>-0.1921423575261517</v>
+      </c>
+      <c r="I57">
+        <v>23.86485404968262</v>
+      </c>
+      <c r="J57">
+        <v>23.24953498840332</v>
+      </c>
+      <c r="K57">
+        <v>22.39412231445312</v>
+      </c>
+      <c r="L57">
+        <v>19.12791553497314</v>
+      </c>
+      <c r="M57">
+        <v>1.03</v>
+      </c>
+      <c r="N57">
+        <v>1.07</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
+      <c r="W57" t="b">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>12.59</v>
+      </c>
+      <c r="Y57">
+        <v>25.49</v>
+      </c>
+      <c r="Z57">
+        <v>1.2</v>
+      </c>
+      <c r="AA57">
+        <v>-2.67</v>
+      </c>
+      <c r="AB57">
+        <v>40.89</v>
+      </c>
+      <c r="AC57">
+        <v>28.25</v>
+      </c>
+      <c r="AD57">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="AE57">
+        <v>7.81</v>
+      </c>
+      <c r="AF57">
+        <v>-4.19</v>
+      </c>
+      <c r="AG57">
+        <v>24.16</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI57" t="s">
+        <v>143</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>178</v>
+      </c>
+      <c r="AK57">
+        <v>30.09871374970599</v>
+      </c>
+    </row>
+    <row r="58" spans="1:37">
+      <c r="A58" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58">
+        <v>93.85346953152518</v>
+      </c>
+      <c r="C58">
+        <v>3192</v>
+      </c>
+      <c r="D58">
+        <v>77.16</v>
+      </c>
+      <c r="E58">
+        <v>1.69</v>
+      </c>
+      <c r="F58">
+        <v>-1.000608240734538</v>
+      </c>
+      <c r="G58">
+        <v>1.59</v>
+      </c>
+      <c r="H58">
+        <v>-1.363886367027739</v>
+      </c>
+      <c r="I58">
+        <v>75.59493560791016</v>
+      </c>
+      <c r="J58">
+        <v>75.70374412536621</v>
+      </c>
+      <c r="K58">
+        <v>69.7171997833252</v>
+      </c>
+      <c r="L58">
+        <v>62.51267461776733</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>1.08</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <v>1</v>
+      </c>
+      <c r="V58" t="b">
+        <v>1</v>
+      </c>
+      <c r="W58" t="b">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>35.66</v>
+      </c>
+      <c r="Y58">
+        <v>78.81999999999999</v>
+      </c>
+      <c r="Z58">
+        <v>1.61</v>
+      </c>
+      <c r="AA58">
+        <v>22.62</v>
+      </c>
+      <c r="AB58">
+        <v>10.91</v>
+      </c>
+      <c r="AC58">
+        <v>39.21</v>
+      </c>
+      <c r="AD58">
+        <v>7.3</v>
+      </c>
+      <c r="AE58">
+        <v>-2.3</v>
+      </c>
+      <c r="AF58">
+        <v>46.9</v>
+      </c>
+      <c r="AG58">
+        <v>-3.01</v>
+      </c>
+      <c r="AH58" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>135</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>179</v>
+      </c>
+      <c r="AK58">
+        <v>30.08060331972925</v>
+      </c>
+    </row>
+    <row r="59" spans="1:37">
+      <c r="A59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59">
+        <v>92.81437125748504</v>
+      </c>
+      <c r="C59">
+        <v>3077</v>
+      </c>
+      <c r="D59">
+        <v>179.99</v>
+      </c>
+      <c r="E59">
+        <v>1.97</v>
+      </c>
+      <c r="F59">
+        <v>-0.7098614936900006</v>
+      </c>
+      <c r="G59">
+        <v>2.04</v>
+      </c>
+      <c r="H59">
+        <v>-0.7714315307628914</v>
+      </c>
+      <c r="I59">
+        <v>175.9800018310547</v>
+      </c>
+      <c r="J59">
+        <v>181.7149993896484</v>
+      </c>
+      <c r="K59">
+        <v>164.2695999145508</v>
+      </c>
+      <c r="L59">
+        <v>151.7505001068115</v>
+      </c>
+      <c r="M59">
+        <v>0.97</v>
+      </c>
+      <c r="N59">
+        <v>1.07</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59" t="b">
+        <v>0</v>
+      </c>
+      <c r="V59" t="b">
+        <v>0</v>
+      </c>
+      <c r="W59" t="b">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>89.52</v>
+      </c>
+      <c r="Y59">
+        <v>190.29</v>
+      </c>
+      <c r="Z59">
+        <v>6.12</v>
+      </c>
+      <c r="AA59">
+        <v>57.62</v>
+      </c>
+      <c r="AB59">
+        <v>34.63</v>
+      </c>
+      <c r="AC59">
+        <v>28.4</v>
+      </c>
+      <c r="AD59">
+        <v>5.16</v>
+      </c>
+      <c r="AE59">
+        <v>-0.95</v>
+      </c>
+      <c r="AF59">
+        <v>15.38</v>
+      </c>
+      <c r="AG59">
+        <v>12.35</v>
+      </c>
+      <c r="AH59" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>172</v>
+      </c>
+      <c r="AK59">
+        <v>29.79601845426408</v>
+      </c>
+    </row>
+    <row r="60" spans="1:37">
+      <c r="A60" t="s">
+        <v>95</v>
+      </c>
+      <c r="B60">
+        <v>91.1060232476224</v>
+      </c>
+      <c r="C60">
+        <v>2032</v>
+      </c>
+      <c r="D60">
+        <v>74.14</v>
+      </c>
+      <c r="E60">
+        <v>2.14</v>
+      </c>
+      <c r="F60">
+        <v>-0.5333366829843886</v>
+      </c>
+      <c r="G60">
+        <v>2.23</v>
+      </c>
+      <c r="H60">
+        <v>-0.5212839332288447</v>
+      </c>
+      <c r="I60">
+        <v>69.86313934326172</v>
+      </c>
+      <c r="J60">
+        <v>69.00340118408204</v>
+      </c>
+      <c r="K60">
+        <v>64.39324722290038</v>
+      </c>
+      <c r="L60">
+        <v>63.98448331832886</v>
+      </c>
+      <c r="M60">
+        <v>1.01</v>
+      </c>
+      <c r="N60">
+        <v>1.08</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60" t="b">
+        <v>0</v>
+      </c>
+      <c r="V60" t="b">
+        <v>1</v>
+      </c>
+      <c r="W60" t="b">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>38.96</v>
+      </c>
+      <c r="Y60">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="Z60">
+        <v>2.03</v>
+      </c>
+      <c r="AA60">
+        <v>28.9</v>
+      </c>
+      <c r="AB60">
+        <v>60.46</v>
+      </c>
+      <c r="AC60">
+        <v>22.46</v>
+      </c>
+      <c r="AD60">
+        <v>7.12</v>
+      </c>
+      <c r="AE60">
+        <v>-3.15</v>
+      </c>
+      <c r="AF60">
+        <v>15.18</v>
+      </c>
+      <c r="AG60">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK60">
+        <v>29.06854794188261</v>
+      </c>
+    </row>
+    <row r="61" spans="1:37">
+      <c r="A61" t="s">
+        <v>96</v>
+      </c>
+      <c r="B61">
+        <v>91.14124691792885</v>
+      </c>
+      <c r="C61">
+        <v>3000</v>
+      </c>
+      <c r="D61">
+        <v>70.05</v>
+      </c>
+      <c r="E61">
+        <v>2.36</v>
+      </c>
+      <c r="F61">
+        <v>-0.3048928103065383</v>
+      </c>
+      <c r="G61">
+        <v>2.04</v>
+      </c>
+      <c r="H61">
+        <v>-0.7714315307628914</v>
+      </c>
+      <c r="I61">
+        <v>70.89358367919922</v>
+      </c>
+      <c r="J61">
+        <v>71.96555252075196</v>
+      </c>
+      <c r="K61">
+        <v>64.90695610046387</v>
+      </c>
+      <c r="L61">
+        <v>56.69324254989624</v>
+      </c>
+      <c r="M61">
+        <v>0.99</v>
+      </c>
+      <c r="N61">
+        <v>1.09</v>
+      </c>
+      <c r="P61">
+        <v>1</v>
+      </c>
+      <c r="Q61">
+        <v>3</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>4</v>
+      </c>
+      <c r="T61">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="U61" t="b">
+        <v>0</v>
+      </c>
+      <c r="V61" t="b">
+        <v>0</v>
+      </c>
+      <c r="W61" t="b">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>37.5</v>
+      </c>
+      <c r="Y61">
+        <v>75.94</v>
+      </c>
+      <c r="Z61">
+        <v>1.17</v>
+      </c>
+      <c r="AA61">
+        <v>24.58</v>
+      </c>
+      <c r="AB61">
+        <v>2.63</v>
+      </c>
+      <c r="AC61">
+        <v>13.79</v>
+      </c>
+      <c r="AD61">
+        <v>10.62</v>
+      </c>
+      <c r="AE61">
+        <v>-2.94</v>
+      </c>
+      <c r="AF61">
+        <v>61.9</v>
+      </c>
+      <c r="AG61">
+        <v>-27.59</v>
+      </c>
+      <c r="AH61" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI61" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>181</v>
+      </c>
+      <c r="AK61">
+        <v>28.9057463300574</v>
+      </c>
+    </row>
+    <row r="62" spans="1:37">
+      <c r="A62" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62">
+        <v>99.27791475871786</v>
+      </c>
+      <c r="C62">
+        <v>2008</v>
+      </c>
+      <c r="D62">
+        <v>31.38</v>
+      </c>
+      <c r="E62">
+        <v>3.04</v>
+      </c>
+      <c r="F62">
+        <v>0.4012064325159093</v>
+      </c>
+      <c r="G62">
+        <v>3.24</v>
+      </c>
+      <c r="H62">
+        <v>0.8084480326100355</v>
+      </c>
+      <c r="I62">
+        <v>30.24266624450684</v>
+      </c>
+      <c r="J62">
+        <v>30.92840976715088</v>
+      </c>
+      <c r="K62">
+        <v>27.26613368988037</v>
+      </c>
+      <c r="L62">
+        <v>19.10543988704681</v>
+      </c>
+      <c r="M62">
+        <v>0.98</v>
+      </c>
+      <c r="N62">
+        <v>1.11</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>1</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>1</v>
+      </c>
+      <c r="T62">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U62" t="b">
+        <v>0</v>
+      </c>
+      <c r="V62" t="b">
+        <v>1</v>
+      </c>
+      <c r="W62" t="b">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>5.27</v>
+      </c>
+      <c r="Y62">
+        <v>33.9</v>
+      </c>
+      <c r="Z62">
+        <v>1.01</v>
+      </c>
+      <c r="AA62">
+        <v>46.89</v>
+      </c>
+      <c r="AB62">
+        <v>87.84</v>
+      </c>
+      <c r="AC62">
+        <v>13.16</v>
+      </c>
+      <c r="AD62">
+        <v>8.74</v>
+      </c>
+      <c r="AE62">
+        <v>4.88</v>
+      </c>
+      <c r="AF62">
+        <v>141.18</v>
+      </c>
+      <c r="AG62">
+        <v>-55.26</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI62" t="s">
+        <v>139</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>182</v>
+      </c>
+      <c r="AK62">
+        <v>28.18819939620453</v>
+      </c>
+    </row>
+    <row r="63" spans="1:37">
+      <c r="A63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B63">
+        <v>93.16660796054948</v>
+      </c>
+      <c r="C63">
+        <v>2408</v>
+      </c>
+      <c r="D63">
+        <v>86.72</v>
+      </c>
+      <c r="E63">
+        <v>2.09</v>
+      </c>
+      <c r="F63">
+        <v>-0.5852557449566277</v>
+      </c>
+      <c r="G63">
+        <v>2.89</v>
+      </c>
+      <c r="H63">
+        <v>0.3476498266262651</v>
+      </c>
+      <c r="I63">
+        <v>88.40963745117188</v>
+      </c>
+      <c r="J63">
+        <v>92.98098106384278</v>
+      </c>
+      <c r="K63">
+        <v>79.48477485656738</v>
+      </c>
+      <c r="L63">
+        <v>64.91940366744996</v>
+      </c>
+      <c r="M63">
+        <v>0.95</v>
+      </c>
+      <c r="N63">
+        <v>1.11</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>4</v>
+      </c>
+      <c r="T63">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="U63" t="b">
+        <v>0</v>
+      </c>
+      <c r="V63" t="b">
+        <v>0</v>
+      </c>
+      <c r="W63" t="b">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>38.04</v>
+      </c>
+      <c r="Y63">
+        <v>98.86</v>
+      </c>
+      <c r="Z63">
+        <v>2.84</v>
+      </c>
+      <c r="AA63">
+        <v>258.51</v>
+      </c>
+      <c r="AB63">
+        <v>139.88</v>
+      </c>
+      <c r="AC63">
+        <v>6.85</v>
+      </c>
+      <c r="AD63">
+        <v>4.91</v>
+      </c>
+      <c r="AE63">
+        <v>-47.3</v>
+      </c>
+      <c r="AF63">
+        <v>60.87</v>
+      </c>
+      <c r="AG63">
+        <v>26.03</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI63" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK63">
+        <v>27.81863048651326</v>
+      </c>
+    </row>
+    <row r="64" spans="1:37">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64">
+        <v>91.37020077492075</v>
+      </c>
+      <c r="C64">
+        <v>3325</v>
+      </c>
+      <c r="D64">
+        <v>31.01</v>
+      </c>
+      <c r="E64">
+        <v>1.59</v>
+      </c>
+      <c r="F64">
+        <v>-1.104446364679015</v>
+      </c>
+      <c r="G64">
+        <v>1.58</v>
+      </c>
+      <c r="H64">
+        <v>-1.377052030055846</v>
+      </c>
+      <c r="I64">
+        <v>30.27104949951172</v>
+      </c>
+      <c r="J64">
+        <v>31.43309850692749</v>
+      </c>
+      <c r="K64">
+        <v>30.11966152191162</v>
+      </c>
+      <c r="L64">
+        <v>25.87754574775696</v>
+      </c>
+      <c r="M64">
+        <v>0.96</v>
+      </c>
+      <c r="N64">
+        <v>1.01</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64" t="b">
+        <v>0</v>
+      </c>
+      <c r="V64" t="b">
+        <v>0</v>
+      </c>
+      <c r="W64" t="b">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>16.15</v>
+      </c>
+      <c r="Y64">
+        <v>32.62</v>
+      </c>
+      <c r="Z64">
+        <v>1.1</v>
+      </c>
+      <c r="AA64">
+        <v>35.16</v>
+      </c>
+      <c r="AB64">
+        <v>29.58</v>
+      </c>
+      <c r="AC64">
+        <v>22.73</v>
+      </c>
+      <c r="AD64">
+        <v>3.25</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>-2.41</v>
+      </c>
+      <c r="AG64">
+        <v>25.76</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI64" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK64">
+        <v>27.67416224008842</v>
+      </c>
+    </row>
+    <row r="65" spans="1:37">
+      <c r="A65" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65">
+        <v>90.57766819302572</v>
+      </c>
+      <c r="C65">
+        <v>3805</v>
+      </c>
+      <c r="D65">
+        <v>232.42</v>
+      </c>
+      <c r="E65">
+        <v>1.64</v>
+      </c>
+      <c r="F65">
+        <v>-1.052527302706777</v>
+      </c>
+      <c r="G65">
+        <v>1.66</v>
+      </c>
+      <c r="H65">
+        <v>-1.271726725830985</v>
+      </c>
+      <c r="I65">
+        <v>231.4251922607422</v>
+      </c>
+      <c r="J65">
+        <v>228.9113830566406</v>
+      </c>
+      <c r="K65">
+        <v>216.9535440063477</v>
+      </c>
+      <c r="L65">
+        <v>189.2392610168457</v>
+      </c>
+      <c r="M65">
+        <v>1.01</v>
+      </c>
+      <c r="N65">
+        <v>1.07</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65" t="b">
+        <v>1</v>
+      </c>
+      <c r="V65" t="b">
+        <v>1</v>
+      </c>
+      <c r="W65" t="b">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>126.33</v>
+      </c>
+      <c r="Y65">
+        <v>236.82</v>
+      </c>
+      <c r="Z65">
+        <v>2.34</v>
+      </c>
+      <c r="AA65">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AB65">
+        <v>18.13</v>
+      </c>
+      <c r="AC65">
+        <v>25.53</v>
+      </c>
+      <c r="AD65">
+        <v>3.81</v>
+      </c>
+      <c r="AE65">
+        <v>-10.15</v>
+      </c>
+      <c r="AF65">
+        <v>37.76</v>
+      </c>
+      <c r="AG65">
+        <v>1.42</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>159</v>
+      </c>
+      <c r="AK65">
+        <v>27.60740003430305</v>
+      </c>
+    </row>
+    <row r="66" spans="1:37">
+      <c r="A66" t="s">
+        <v>101</v>
+      </c>
+      <c r="B66">
+        <v>93.69496301514619</v>
+      </c>
+      <c r="C66">
+        <v>3328</v>
+      </c>
+      <c r="D66">
+        <v>111.99</v>
+      </c>
+      <c r="E66">
+        <v>2.52</v>
+      </c>
+      <c r="F66">
+        <v>-0.138751811995374</v>
+      </c>
+      <c r="G66">
+        <v>2.12</v>
+      </c>
+      <c r="H66">
+        <v>-0.6661062265380295</v>
+      </c>
+      <c r="I66">
+        <v>112.9099990844727</v>
+      </c>
+      <c r="J66">
+        <v>114.036499786377</v>
+      </c>
+      <c r="K66">
+        <v>108.0273999023437</v>
+      </c>
+      <c r="L66">
+        <v>90.62624988555908</v>
+      </c>
+      <c r="M66">
+        <v>0.99</v>
+      </c>
+      <c r="N66">
+        <v>1.05</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" t="b">
+        <v>0</v>
+      </c>
+      <c r="V66" t="b">
+        <v>0</v>
+      </c>
+      <c r="W66" t="b">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>52.49</v>
+      </c>
+      <c r="Y66">
+        <v>121.22</v>
+      </c>
+      <c r="Z66">
+        <v>1.71</v>
+      </c>
+      <c r="AA66">
+        <v>41.32</v>
+      </c>
+      <c r="AB66">
+        <v>14.22</v>
+      </c>
+      <c r="AC66">
+        <v>26.85</v>
+      </c>
+      <c r="AD66">
+        <v>4.67</v>
+      </c>
+      <c r="AE66">
+        <v>8.73</v>
+      </c>
+      <c r="AF66">
+        <v>5.88</v>
+      </c>
+      <c r="AG66">
+        <v>10.19</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI66" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK66">
+        <v>27.5261749007544</v>
+      </c>
+    </row>
+    <row r="67" spans="1:37">
+      <c r="A67" t="s">
+        <v>102</v>
+      </c>
+      <c r="B67">
+        <v>91.72243747798521</v>
+      </c>
+      <c r="C67">
+        <v>1123</v>
+      </c>
+      <c r="D67">
+        <v>181.24</v>
+      </c>
+      <c r="E67">
+        <v>1.44</v>
+      </c>
+      <c r="F67">
+        <v>-1.260203550595732</v>
+      </c>
+      <c r="G67">
+        <v>1.51</v>
+      </c>
+      <c r="H67">
+        <v>-1.469211671252601</v>
+      </c>
+      <c r="I67">
+        <v>177.6606842041016</v>
+      </c>
+      <c r="J67">
+        <v>176.4170555114746</v>
+      </c>
+      <c r="K67">
+        <v>166.1750833129883</v>
+      </c>
+      <c r="L67">
+        <v>143.938404006958</v>
+      </c>
+      <c r="M67">
+        <v>1.01</v>
+      </c>
+      <c r="N67">
+        <v>1.07</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U67" t="b">
+        <v>1</v>
+      </c>
+      <c r="V67" t="b">
+        <v>1</v>
+      </c>
+      <c r="W67" t="b">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>92.09</v>
+      </c>
+      <c r="Y67">
+        <v>183.13</v>
+      </c>
+      <c r="Z67">
+        <v>20.81</v>
+      </c>
+      <c r="AA67">
+        <v>12.04</v>
+      </c>
+      <c r="AB67">
+        <v>17.47</v>
+      </c>
+      <c r="AC67">
+        <v>19.49</v>
+      </c>
+      <c r="AD67">
+        <v>5.91</v>
+      </c>
+      <c r="AE67">
+        <v>12.8</v>
+      </c>
+      <c r="AF67">
+        <v>-18.83</v>
+      </c>
+      <c r="AG67">
+        <v>30.51</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK67">
+        <v>25.88026847445132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:37">
+      <c r="A68" t="s">
+        <v>103</v>
+      </c>
+      <c r="B68">
+        <v>94.57555477280732</v>
+      </c>
+      <c r="C68">
+        <v>1414</v>
+      </c>
+      <c r="D68">
+        <v>74.02</v>
+      </c>
+      <c r="E68">
+        <v>2.45</v>
+      </c>
+      <c r="F68">
+        <v>-0.2114384987565082</v>
+      </c>
+      <c r="G68">
+        <v>2.46</v>
+      </c>
+      <c r="H68">
+        <v>-0.2184736835823671</v>
+      </c>
+      <c r="I68">
+        <v>73.50799865722657</v>
+      </c>
+      <c r="J68">
+        <v>76.98799934387208</v>
+      </c>
+      <c r="K68">
+        <v>71.14299949645996</v>
+      </c>
+      <c r="L68">
+        <v>65.65519958496094</v>
+      </c>
+      <c r="M68">
+        <v>0.95</v>
+      </c>
+      <c r="N68">
+        <v>1.03</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68" t="b">
+        <v>0</v>
+      </c>
+      <c r="V68" t="b">
+        <v>0</v>
+      </c>
+      <c r="W68" t="b">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>32.49</v>
+      </c>
+      <c r="Y68">
+        <v>83.69</v>
+      </c>
+      <c r="Z68">
+        <v>7.23</v>
+      </c>
+      <c r="AA68">
+        <v>-23.78</v>
+      </c>
+      <c r="AB68">
+        <v>169.68</v>
+      </c>
+      <c r="AC68">
+        <v>6.62</v>
+      </c>
+      <c r="AD68">
+        <v>35.29</v>
+      </c>
+      <c r="AE68">
+        <v>277.48</v>
+      </c>
+      <c r="AF68">
+        <v>21.98</v>
+      </c>
+      <c r="AG68">
+        <v>-76.84</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>183</v>
+      </c>
+      <c r="AK68">
+        <v>21.82523356315006</v>
+      </c>
+    </row>
+    <row r="69" spans="1:37">
+      <c r="A69" t="s">
+        <v>104</v>
+      </c>
+      <c r="B69">
+        <v>92.26840436773512</v>
+      </c>
+      <c r="C69">
+        <v>572</v>
+      </c>
+      <c r="D69">
+        <v>49.82</v>
+      </c>
+      <c r="E69">
+        <v>2.24</v>
+      </c>
+      <c r="F69">
+        <v>-0.429498559039911</v>
+      </c>
+      <c r="G69">
+        <v>2.11</v>
+      </c>
+      <c r="H69">
+        <v>-0.6792718895661375</v>
+      </c>
+      <c r="I69">
+        <v>49.65778274536133</v>
+      </c>
+      <c r="J69">
+        <v>52.16899337768555</v>
+      </c>
+      <c r="K69">
+        <v>48.57435165405273</v>
+      </c>
+      <c r="L69">
+        <v>41.22910265922546</v>
+      </c>
+      <c r="M69">
+        <v>0.95</v>
+      </c>
+      <c r="N69">
+        <v>1.02</v>
+      </c>
+      <c r="P69">
+        <v>1</v>
+      </c>
+      <c r="Q69">
+        <v>7</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="U69" t="b">
+        <v>0</v>
+      </c>
+      <c r="V69" t="b">
+        <v>0</v>
+      </c>
+      <c r="W69" t="b">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>25.34</v>
+      </c>
+      <c r="Y69">
+        <v>54.71</v>
+      </c>
+      <c r="Z69">
+        <v>15.5</v>
+      </c>
+      <c r="AA69">
+        <v>-13305.79</v>
+      </c>
+      <c r="AB69">
+        <v>847.0599999999999</v>
+      </c>
+      <c r="AC69">
+        <v>0.67</v>
+      </c>
+      <c r="AD69">
+        <v>10.88</v>
+      </c>
+      <c r="AE69">
+        <v>-42.53</v>
+      </c>
+      <c r="AF69">
+        <v>6.53</v>
+      </c>
+      <c r="AG69">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI69" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK69">
+        <v>20.21912017515939</v>
+      </c>
+    </row>
+    <row r="70" spans="1:37">
+      <c r="A70" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70">
+        <v>91.68721380767876</v>
+      </c>
+      <c r="C70">
+        <v>3650</v>
+      </c>
+      <c r="D70">
+        <v>156.59</v>
+      </c>
+      <c r="E70">
+        <v>2.23</v>
+      </c>
+      <c r="F70">
+        <v>-0.439882371434359</v>
+      </c>
+      <c r="G70">
+        <v>2.2</v>
+      </c>
+      <c r="H70">
+        <v>-0.5607809223131676</v>
+      </c>
+      <c r="I70">
+        <v>155.1528961181641</v>
+      </c>
+      <c r="J70">
+        <v>162.3704216003418</v>
+      </c>
+      <c r="K70">
+        <v>148.5521209716797</v>
+      </c>
+      <c r="L70">
+        <v>120.5036893463135</v>
+      </c>
+      <c r="M70">
+        <v>0.96</v>
+      </c>
+      <c r="N70">
+        <v>1.04</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70" t="b">
+        <v>0</v>
+      </c>
+      <c r="V70" t="b">
+        <v>0</v>
+      </c>
+      <c r="W70" t="b">
+        <v>1</v>
+      </c>
+      <c r="X70">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="Y70">
+        <v>173.96</v>
+      </c>
+      <c r="Z70">
+        <v>2.12</v>
+      </c>
+      <c r="AA70">
+        <v>-433.67</v>
+      </c>
+      <c r="AB70">
+        <v>158.05</v>
+      </c>
+      <c r="AC70">
+        <v>5.23</v>
+      </c>
+      <c r="AD70">
+        <v>4.69</v>
+      </c>
+      <c r="AE70">
+        <v>-33.74</v>
+      </c>
+      <c r="AF70">
+        <v>41.28</v>
+      </c>
+      <c r="AG70">
+        <v>12.42</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI70" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK70">
+        <v>19.98674678970162</v>
       </c>
     </row>
   </sheetData>
